--- a/Планирование_спринта_PRO.xlsx
+++ b/Планирование_спринта_PRO.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="733" firstSheet="0" activeTab="8" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="733" firstSheet="0" activeTab="6" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Дашборды" sheetId="1" state="visible" r:id="rId1"/>
@@ -37,6 +37,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Матрица рисков" sheetId="29" state="visible" r:id="rId29"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Распределение" sheetId="30" state="visible" r:id="rId30"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Time to Market" sheetId="31" state="visible" r:id="rId31"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FAQ" sheetId="32" state="visible" r:id="rId32"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
@@ -360,7 +361,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="55">
+  <fills count="57">
     <fill>
       <patternFill/>
     </fill>
@@ -632,8 +633,18 @@
         <fgColor rgb="FFE4E9F0"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDDEBF7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEADAF3"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="20">
+  <borders count="21">
     <border>
       <left/>
       <right/>
@@ -876,6 +887,21 @@
       <diagonal/>
     </border>
     <border>
+      <left style="thin">
+        <color rgb="FFD9D9D9"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFD9D9D9"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFD9D9D9"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFD9D9D9"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left/>
       <right/>
       <top style="thin">
@@ -913,7 +939,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="257">
+  <cellXfs count="264">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -1493,38 +1519,59 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="48" fillId="48" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="16" fillId="13" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="39" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="48" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="17" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="17" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="48" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="51" borderId="17" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="52" borderId="17" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="53" borderId="17" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="54" borderId="17" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="16" fillId="13" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="39" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="13" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="48" fillId="48" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="48" fillId="48" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="19" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="19" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="6" fillId="55" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="48" fillId="48" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="51" borderId="19" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="52" borderId="19" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="53" borderId="19" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="54" borderId="19" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="40" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="47" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="56" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -1694,6 +1741,34 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
+          <fgColor rgb="FFE4E9F0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFD6E4FB"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFDECC8"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8D2D2"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
           <fgColor rgb="FFF8D7DA"/>
         </patternFill>
       </fill>
@@ -1856,34 +1931,6 @@
       <fill>
         <patternFill patternType="solid">
           <fgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8D2D2"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFDECC8"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFD6E4FB"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFE4E9F0"/>
         </patternFill>
       </fill>
     </dxf>
@@ -13827,27 +13874,42 @@
       <tx>
         <rich>
           <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
           <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>Число фич по категориям MoSCoW</a:t>
+              <a:rPr lang="ru-RU"/>
+              <a:t xml:space="preserve">Число фич по категориям </a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="en-US"/>
+              <a:t>MoSCoW</a:t>
             </a:r>
           </a:p>
         </rich>
       </tx>
+      <overlay val="1"/>
     </title>
     <plotArea>
+      <layout/>
       <barChart>
         <barDir val="bar"/>
         <grouping val="clustered"/>
+        <varyColors val="1"/>
         <ser>
           <idx val="0"/>
           <order val="0"/>
           <tx>
             <strRef>
-              <f>'MoSCoW'!B19</f>
+              <f>MoSCoW!$B$19</f>
+              <strCache>
+                <ptCount val="1"/>
+                <pt idx="0">
+                  <v>Кол-во</v>
+                </pt>
+              </strCache>
             </strRef>
           </tx>
           <spPr>
@@ -13855,17 +13917,57 @@
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
+          <invertIfNegative val="1"/>
           <cat>
-            <numRef>
-              <f>'MoSCoW'!$A$20:$A$23</f>
-            </numRef>
+            <strRef>
+              <f>MoSCoW!$A$20:$A$23</f>
+              <strCache>
+                <ptCount val="4"/>
+                <pt idx="0">
+                  <v>Must</v>
+                </pt>
+                <pt idx="1">
+                  <v>Should</v>
+                </pt>
+                <pt idx="2">
+                  <v>Could</v>
+                </pt>
+                <pt idx="3">
+                  <v>Won't</v>
+                </pt>
+              </strCache>
+            </strRef>
           </cat>
           <val>
             <numRef>
-              <f>'MoSCoW'!$B$20:$B$23</f>
+              <f>MoSCoW!$B$20:$B$23</f>
+              <numCache>
+                <formatCode>General</formatCode>
+                <ptCount val="4"/>
+                <pt idx="0">
+                  <v>4</v>
+                </pt>
+                <pt idx="1">
+                  <v>3</v>
+                </pt>
+                <pt idx="2">
+                  <v>3</v>
+                </pt>
+                <pt idx="3">
+                  <v>2</v>
+                </pt>
+              </numCache>
             </numRef>
           </val>
         </ser>
+        <dLbls>
+          <showLegendKey val="0"/>
+          <showVal val="0"/>
+          <showCatName val="0"/>
+          <showSerName val="0"/>
+          <showPercent val="0"/>
+          <showBubbleSize val="0"/>
+        </dLbls>
         <gapWidth val="150"/>
         <axId val="10"/>
         <axId val="100"/>
@@ -13877,10 +13979,16 @@
         </scaling>
         <delete val="0"/>
         <axPos val="l"/>
+        <numFmt formatCode="General" sourceLinked="1"/>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
+        <tickLblPos val="nextTo"/>
         <crossAx val="100"/>
+        <crosses val="autoZero"/>
+        <auto val="1"/>
+        <lblAlgn val="ctr"/>
         <lblOffset val="100"/>
+        <noMultiLvlLbl val="1"/>
       </catAx>
       <valAx>
         <axId val="100"/>
@@ -13888,11 +13996,15 @@
           <orientation val="minMax"/>
         </scaling>
         <delete val="0"/>
-        <axPos val="l"/>
+        <axPos val="b"/>
         <majorGridlines/>
+        <numFmt formatCode="General" sourceLinked="1"/>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
+        <tickLblPos val="nextTo"/>
         <crossAx val="10"/>
+        <crosses val="autoZero"/>
+        <crossBetween val="between"/>
       </valAx>
     </plotArea>
     <plotVisOnly val="1"/>
@@ -25909,8 +26021,8 @@
     <from>
       <col>6</col>
       <colOff>0</colOff>
-      <row>3</row>
-      <rowOff>0</rowOff>
+      <row>4</row>
+      <rowOff>167640</rowOff>
     </from>
     <ext cx="4680000" cy="2340000"/>
     <graphicFrame>
@@ -36400,13 +36512,13 @@
           <t>Цель спринта:</t>
         </is>
       </c>
-      <c r="B3" s="245">
+      <c r="B3" s="253">
         <f>Параметры!$B$19</f>
         <v/>
       </c>
-      <c r="C3" s="242" t="n"/>
-      <c r="D3" s="242" t="n"/>
-      <c r="E3" s="243" t="n"/>
+      <c r="C3" s="254" t="n"/>
+      <c r="D3" s="254" t="n"/>
+      <c r="E3" s="255" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="38" t="inlineStr">
@@ -46574,6 +46686,370 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet32.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D18"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="40" customWidth="1" min="3" max="3"/>
+    <col width="66" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="213" t="inlineStr">
+        <is>
+          <t>FAQ — частые вопросы по приложению</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="225" t="inlineStr">
+        <is>
+          <t>Ответы на типичные вопросы о работе с приложением планирования спринтов.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="256" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B4" s="256" t="inlineStr">
+        <is>
+          <t>Категория</t>
+        </is>
+      </c>
+      <c r="C4" s="256" t="inlineStr">
+        <is>
+          <t>Вопрос</t>
+        </is>
+      </c>
+      <c r="D4" s="256" t="inlineStr">
+        <is>
+          <t>Ответ</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="46" customHeight="1">
+      <c r="A5" s="257" t="inlineStr">
+        <is>
+          <t>Q-01</t>
+        </is>
+      </c>
+      <c r="B5" s="258" t="inlineStr">
+        <is>
+          <t>Начало работы</t>
+        </is>
+      </c>
+      <c r="C5" s="259" t="inlineStr">
+        <is>
+          <t>С чего начать работу в приложении?</t>
+        </is>
+      </c>
+      <c r="D5" s="260" t="inlineStr">
+        <is>
+          <t>Заполните «Параметры» (даты старта, число спринтов, focus factor), затем «Команду» и «Бэклог». Дорожная карта, ёмкость, velocity, релизы и метрики считаются автоматически из этих данных.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="46" customHeight="1">
+      <c r="A6" s="257" t="inlineStr">
+        <is>
+          <t>Q-02</t>
+        </is>
+      </c>
+      <c r="B6" s="258" t="inlineStr">
+        <is>
+          <t>Начало работы</t>
+        </is>
+      </c>
+      <c r="C6" s="259" t="inlineStr">
+        <is>
+          <t>Нужен ли интернет или сервер?</t>
+        </is>
+      </c>
+      <c r="D6" s="260" t="inlineStr">
+        <is>
+          <t>Нет. Приложение работает локально в браузере, данные хранятся в localStorage. Если поднят backend (Java + Python), состояние синхронизируется через /api/state.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="46" customHeight="1">
+      <c r="A7" s="257" t="inlineStr">
+        <is>
+          <t>Q-03</t>
+        </is>
+      </c>
+      <c r="B7" s="258" t="inlineStr">
+        <is>
+          <t>Начало работы</t>
+        </is>
+      </c>
+      <c r="C7" s="259" t="inlineStr">
+        <is>
+          <t>Как быстро найти нужный раздел или действие?</t>
+        </is>
+      </c>
+      <c r="D7" s="260" t="inlineStr">
+        <is>
+          <t>Нажмите Ctrl/⌘+K — откроется командная палитра с поиском по всем разделам и действиям.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="46" customHeight="1">
+      <c r="A8" s="257" t="inlineStr">
+        <is>
+          <t>Q-04</t>
+        </is>
+      </c>
+      <c r="B8" s="261" t="inlineStr">
+        <is>
+          <t>Планирование</t>
+        </is>
+      </c>
+      <c r="C8" s="259" t="inlineStr">
+        <is>
+          <t>Как рассчитывается ёмкость спринта?</t>
+        </is>
+      </c>
+      <c r="D8" s="260" t="inlineStr">
+        <is>
+          <t>Из состава «Команды» и её доступности, отсутствий, числа рабочих дней спринта (с учётом «Календаря» праздников) и focus factor из «Параметров».</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="46" customHeight="1">
+      <c r="A9" s="257" t="inlineStr">
+        <is>
+          <t>Q-05</t>
+        </is>
+      </c>
+      <c r="B9" s="261" t="inlineStr">
+        <is>
+          <t>Планирование</t>
+        </is>
+      </c>
+      <c r="C9" s="259" t="inlineStr">
+        <is>
+          <t>Что такое focus factor?</t>
+        </is>
+      </c>
+      <c r="D9" s="260" t="inlineStr">
+        <is>
+          <t>Доля рабочего времени, реально уходящая на задачи спринта (обычно 0.7–0.8). Остаток — митинги, поддержка, переключения между задачами.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="46" customHeight="1">
+      <c r="A10" s="257" t="inlineStr">
+        <is>
+          <t>Q-06</t>
+        </is>
+      </c>
+      <c r="B10" s="261" t="inlineStr">
+        <is>
+          <t>Планирование</t>
+        </is>
+      </c>
+      <c r="C10" s="259" t="inlineStr">
+        <is>
+          <t>Чем отличаются RICE и MoSCoW?</t>
+        </is>
+      </c>
+      <c r="D10" s="260" t="inlineStr">
+        <is>
+          <t>RICE даёт числовой балл (Reach × Impact × Confidence / Effort) для ранжирования. MoSCoW распределяет фичи по категориям Must / Should / Could / Won't. Их удобно использовать вместе.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="46" customHeight="1">
+      <c r="A11" s="257" t="inlineStr">
+        <is>
+          <t>Q-07</t>
+        </is>
+      </c>
+      <c r="B11" s="262" t="inlineStr">
+        <is>
+          <t>Данные и доступ</t>
+        </is>
+      </c>
+      <c r="C11" s="259" t="inlineStr">
+        <is>
+          <t>Где хранятся мои данные?</t>
+        </is>
+      </c>
+      <c r="D11" s="260" t="inlineStr">
+        <is>
+          <t>Локально в браузере (localStorage) и, если настроен сервер, в базе PostgreSQL через /api/state. Для резервной копии выгружайте JSON или Excel.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="46" customHeight="1">
+      <c r="A12" s="257" t="inlineStr">
+        <is>
+          <t>Q-08</t>
+        </is>
+      </c>
+      <c r="B12" s="262" t="inlineStr">
+        <is>
+          <t>Данные и доступ</t>
+        </is>
+      </c>
+      <c r="C12" s="259" t="inlineStr">
+        <is>
+          <t>Как перенести данные на другой компьютер?</t>
+        </is>
+      </c>
+      <c r="D12" s="260" t="inlineStr">
+        <is>
+          <t>На текущем компьютере нажмите «JSON» (экспорт), на другом — «Импорт» и выберите файл. Импорт доступен администратору.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="46" customHeight="1">
+      <c r="A13" s="257" t="inlineStr">
+        <is>
+          <t>Q-09</t>
+        </is>
+      </c>
+      <c r="B13" s="262" t="inlineStr">
+        <is>
+          <t>Данные и доступ</t>
+        </is>
+      </c>
+      <c r="C13" s="259" t="inlineStr">
+        <is>
+          <t>Что делает кнопка «Сброс»?</t>
+        </is>
+      </c>
+      <c r="D13" s="260" t="inlineStr">
+        <is>
+          <t>Возвращает данные к исходному демонстрационному набору. Действие необратимо и доступно только администратору — перед сбросом сделайте экспорт JSON.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="46" customHeight="1">
+      <c r="A14" s="257" t="inlineStr">
+        <is>
+          <t>Q-10</t>
+        </is>
+      </c>
+      <c r="B14" s="262" t="inlineStr">
+        <is>
+          <t>Данные и доступ</t>
+        </is>
+      </c>
+      <c r="C14" s="259" t="inlineStr">
+        <is>
+          <t>Чем отличаются режимы Просмотр, Редактор и Администратор?</t>
+        </is>
+      </c>
+      <c r="D14" s="260" t="inlineStr">
+        <is>
+          <t>Просмотр — только чтение. Редактор правит данные, кроме «Параметров», «Сброса» и «Импорта». Администратор — полный доступ, включая коды доступа.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="46" customHeight="1">
+      <c r="A15" s="257" t="inlineStr">
+        <is>
+          <t>Q-11</t>
+        </is>
+      </c>
+      <c r="B15" s="262" t="inlineStr">
+        <is>
+          <t>Данные и доступ</t>
+        </is>
+      </c>
+      <c r="C15" s="259" t="inlineStr">
+        <is>
+          <t>Как сменить режим доступа?</t>
+        </is>
+      </c>
+      <c r="D15" s="260" t="inlineStr">
+        <is>
+          <t>Кнопка режима в шапке. Переход в «Редактор» или «Администратор» — по коду, который задаёт администратор в панели «Коды доступа».</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="46" customHeight="1">
+      <c r="A16" s="257" t="inlineStr">
+        <is>
+          <t>Q-12</t>
+        </is>
+      </c>
+      <c r="B16" s="263" t="inlineStr">
+        <is>
+          <t>Экспорт и интерфейс</t>
+        </is>
+      </c>
+      <c r="C16" s="259" t="inlineStr">
+        <is>
+          <t>Как выгрузить план в Excel?</t>
+        </is>
+      </c>
+      <c r="D16" s="260" t="inlineStr">
+        <is>
+          <t>Кнопка «Excel» в шапке или Ctrl/⌘+K → «Экспорт в Excel». Файл включает все разделы, в том числе RICE, MoSCoW и FAQ.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="46" customHeight="1">
+      <c r="A17" s="257" t="inlineStr">
+        <is>
+          <t>Q-13</t>
+        </is>
+      </c>
+      <c r="B17" s="263" t="inlineStr">
+        <is>
+          <t>Экспорт и интерфейс</t>
+        </is>
+      </c>
+      <c r="C17" s="259" t="inlineStr">
+        <is>
+          <t>Есть ли описание и презентация приложения?</t>
+        </is>
+      </c>
+      <c r="D17" s="260" t="inlineStr">
+        <is>
+          <t>Да. К приложению прилагаются документы «Описание…», «Иллюстрированное описание…» (docx) и презентация (pptx).</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="46" customHeight="1">
+      <c r="A18" s="257" t="inlineStr">
+        <is>
+          <t>Q-14</t>
+        </is>
+      </c>
+      <c r="B18" s="263" t="inlineStr">
+        <is>
+          <t>Экспорт и интерфейс</t>
+        </is>
+      </c>
+      <c r="C18" s="259" t="inlineStr">
+        <is>
+          <t>Как свернуть боковое меню?</t>
+        </is>
+      </c>
+      <c r="D18" s="260" t="inlineStr">
+        <is>
+          <t>Кнопка-гамбургер (☰) в шапке сворачивает и разворачивает список разделов; на мобильном — открывает выдвижное меню. Состояние запоминается.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
@@ -48563,7 +49039,7 @@
         <f>IFERROR(E5/D5,0)</f>
         <v/>
       </c>
-      <c r="H5" s="244" t="inlineStr">
+      <c r="H5" s="241" t="inlineStr">
         <is>
           <t>MVP оформления заказа, интеграция оплаты</t>
         </is>
@@ -49246,7 +49722,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:E30"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="32" customWidth="1" min="2" max="2"/>
@@ -49255,7 +49731,7 @@
     <col width="46" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="17.4" customHeight="1">
       <c r="A1" s="213" t="inlineStr">
         <is>
           <t>Приоритизация требований по MoSCoW</t>
@@ -49270,339 +49746,339 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="246" t="inlineStr">
+      <c r="A4" s="242" t="inlineStr">
         <is>
           <t>ID</t>
         </is>
       </c>
-      <c r="B4" s="246" t="inlineStr">
+      <c r="B4" s="242" t="inlineStr">
         <is>
           <t>Фича / требование</t>
         </is>
       </c>
-      <c r="C4" s="246" t="inlineStr">
+      <c r="C4" s="242" t="inlineStr">
         <is>
           <t>Категория</t>
         </is>
       </c>
-      <c r="D4" s="246" t="inlineStr">
+      <c r="D4" s="242" t="inlineStr">
         <is>
           <t>Приоритет</t>
         </is>
       </c>
-      <c r="E4" s="246" t="inlineStr">
+      <c r="E4" s="242" t="inlineStr">
         <is>
           <t>Обоснование</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="247" t="inlineStr">
+      <c r="A5" s="243" t="inlineStr">
         <is>
           <t>MS-01</t>
         </is>
       </c>
-      <c r="B5" s="248" t="inlineStr">
+      <c r="B5" s="244" t="inlineStr">
         <is>
           <t>Оформление заказа (MVP)</t>
         </is>
       </c>
-      <c r="C5" s="249" t="inlineStr">
+      <c r="C5" s="245" t="inlineStr">
         <is>
           <t>Must</t>
         </is>
       </c>
-      <c r="D5" s="250">
+      <c r="D5" s="246">
         <f>IF(C5="Must","Обязательно",IF(C5="Should","Желательно",IF(C5="Could","Возможно",IF(C5="Won't","Не в этот раз",""))))</f>
         <v/>
       </c>
-      <c r="E5" s="251" t="inlineStr">
+      <c r="E5" s="247" t="inlineStr">
         <is>
           <t>Без этого запуск подписки невозможен</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="247" t="inlineStr">
+      <c r="A6" s="243" t="inlineStr">
         <is>
           <t>MS-02</t>
         </is>
       </c>
-      <c r="B6" s="248" t="inlineStr">
+      <c r="B6" s="244" t="inlineStr">
         <is>
           <t>Оплата картой</t>
         </is>
       </c>
-      <c r="C6" s="249" t="inlineStr">
+      <c r="C6" s="245" t="inlineStr">
         <is>
           <t>Must</t>
         </is>
       </c>
-      <c r="D6" s="250">
+      <c r="D6" s="246">
         <f>IF(C6="Must","Обязательно",IF(C6="Should","Желательно",IF(C6="Could","Возможно",IF(C6="Won't","Не в этот раз",""))))</f>
         <v/>
       </c>
-      <c r="E6" s="251" t="inlineStr">
+      <c r="E6" s="247" t="inlineStr">
         <is>
           <t>Ключевой сценарий монетизации</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="247" t="inlineStr">
+      <c r="A7" s="243" t="inlineStr">
         <is>
           <t>MS-03</t>
         </is>
       </c>
-      <c r="B7" s="248" t="inlineStr">
+      <c r="B7" s="244" t="inlineStr">
         <is>
           <t>Каталог товаров и цены</t>
         </is>
       </c>
-      <c r="C7" s="249" t="inlineStr">
+      <c r="C7" s="245" t="inlineStr">
         <is>
           <t>Must</t>
         </is>
       </c>
-      <c r="D7" s="250">
+      <c r="D7" s="246">
         <f>IF(C7="Must","Обязательно",IF(C7="Should","Желательно",IF(C7="Could","Возможно",IF(C7="Won't","Не в этот раз",""))))</f>
         <v/>
       </c>
-      <c r="E7" s="251" t="inlineStr">
+      <c r="E7" s="247" t="inlineStr">
         <is>
           <t>Данные для оформления заказа</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="247" t="inlineStr">
+      <c r="A8" s="243" t="inlineStr">
         <is>
           <t>MS-04</t>
         </is>
       </c>
-      <c r="B8" s="248" t="inlineStr">
+      <c r="B8" s="244" t="inlineStr">
         <is>
           <t>Личный кабинет (базовый)</t>
         </is>
       </c>
-      <c r="C8" s="249" t="inlineStr">
+      <c r="C8" s="245" t="inlineStr">
         <is>
           <t>Must</t>
         </is>
       </c>
-      <c r="D8" s="250">
+      <c r="D8" s="246">
         <f>IF(C8="Must","Обязательно",IF(C8="Should","Желательно",IF(C8="Could","Возможно",IF(C8="Won't","Не в этот раз",""))))</f>
         <v/>
       </c>
-      <c r="E8" s="251" t="inlineStr">
+      <c r="E8" s="247" t="inlineStr">
         <is>
           <t>Управление подпиской</t>
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="247" t="inlineStr">
+    <row r="9" ht="27.6" customHeight="1">
+      <c r="A9" s="243" t="inlineStr">
         <is>
           <t>MS-05</t>
         </is>
       </c>
-      <c r="B9" s="248" t="inlineStr">
+      <c r="B9" s="244" t="inlineStr">
         <is>
           <t>Промокоды и скидки</t>
         </is>
       </c>
-      <c r="C9" s="249" t="inlineStr">
+      <c r="C9" s="245" t="inlineStr">
         <is>
           <t>Should</t>
         </is>
       </c>
-      <c r="D9" s="250">
+      <c r="D9" s="246">
         <f>IF(C9="Must","Обязательно",IF(C9="Should","Желательно",IF(C9="Could","Возможно",IF(C9="Won't","Не в этот раз",""))))</f>
         <v/>
       </c>
-      <c r="E9" s="251" t="inlineStr">
+      <c r="E9" s="247" t="inlineStr">
         <is>
           <t>Повышает конверсию, но релиз возможен без них</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="247" t="inlineStr">
+      <c r="A10" s="243" t="inlineStr">
         <is>
           <t>MS-06</t>
         </is>
       </c>
-      <c r="B10" s="248" t="inlineStr">
+      <c r="B10" s="244" t="inlineStr">
         <is>
           <t>Уведомления (e-mail/push)</t>
         </is>
       </c>
-      <c r="C10" s="249" t="inlineStr">
+      <c r="C10" s="245" t="inlineStr">
         <is>
           <t>Should</t>
         </is>
       </c>
-      <c r="D10" s="250">
+      <c r="D10" s="246">
         <f>IF(C10="Must","Обязательно",IF(C10="Should","Желательно",IF(C10="Could","Возможно",IF(C10="Won't","Не в этот раз",""))))</f>
         <v/>
       </c>
-      <c r="E10" s="251" t="inlineStr">
+      <c r="E10" s="247" t="inlineStr">
         <is>
           <t>Удержание пользователей</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="247" t="inlineStr">
+      <c r="A11" s="243" t="inlineStr">
         <is>
           <t>MS-07</t>
         </is>
       </c>
-      <c r="B11" s="248" t="inlineStr">
+      <c r="B11" s="244" t="inlineStr">
         <is>
           <t>История заказов</t>
         </is>
       </c>
-      <c r="C11" s="249" t="inlineStr">
+      <c r="C11" s="245" t="inlineStr">
         <is>
           <t>Should</t>
         </is>
       </c>
-      <c r="D11" s="250">
+      <c r="D11" s="246">
         <f>IF(C11="Must","Обязательно",IF(C11="Should","Желательно",IF(C11="Could","Возможно",IF(C11="Won't","Не в этот раз",""))))</f>
         <v/>
       </c>
-      <c r="E11" s="251" t="inlineStr">
+      <c r="E11" s="247" t="inlineStr">
         <is>
           <t>Ожидаемо пользователями</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="247" t="inlineStr">
+      <c r="A12" s="243" t="inlineStr">
         <is>
           <t>MS-08</t>
         </is>
       </c>
-      <c r="B12" s="248" t="inlineStr">
+      <c r="B12" s="244" t="inlineStr">
         <is>
           <t>Рекомендации товаров</t>
         </is>
       </c>
-      <c r="C12" s="249" t="inlineStr">
+      <c r="C12" s="245" t="inlineStr">
         <is>
           <t>Could</t>
         </is>
       </c>
-      <c r="D12" s="250">
+      <c r="D12" s="246">
         <f>IF(C12="Must","Обязательно",IF(C12="Should","Желательно",IF(C12="Could","Возможно",IF(C12="Won't","Не в этот раз",""))))</f>
         <v/>
       </c>
-      <c r="E12" s="251" t="inlineStr">
+      <c r="E12" s="247" t="inlineStr">
         <is>
           <t>Если останется время</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="247" t="inlineStr">
+      <c r="A13" s="243" t="inlineStr">
         <is>
           <t>MS-09</t>
         </is>
       </c>
-      <c r="B13" s="248" t="inlineStr">
+      <c r="B13" s="244" t="inlineStr">
         <is>
           <t>Мультиязычность</t>
         </is>
       </c>
-      <c r="C13" s="249" t="inlineStr">
+      <c r="C13" s="245" t="inlineStr">
         <is>
           <t>Could</t>
         </is>
       </c>
-      <c r="D13" s="250">
+      <c r="D13" s="246">
         <f>IF(C13="Must","Обязательно",IF(C13="Should","Желательно",IF(C13="Could","Возможно",IF(C13="Won't","Не в этот раз",""))))</f>
         <v/>
       </c>
-      <c r="E13" s="251" t="inlineStr">
+      <c r="E13" s="247" t="inlineStr">
         <is>
           <t>Для будущих рынков</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="247" t="inlineStr">
+      <c r="A14" s="243" t="inlineStr">
         <is>
           <t>MS-10</t>
         </is>
       </c>
-      <c r="B14" s="248" t="inlineStr">
+      <c r="B14" s="244" t="inlineStr">
         <is>
           <t>Экспорт отчётов</t>
         </is>
       </c>
-      <c r="C14" s="249" t="inlineStr">
+      <c r="C14" s="245" t="inlineStr">
         <is>
           <t>Could</t>
         </is>
       </c>
-      <c r="D14" s="250">
+      <c r="D14" s="246">
         <f>IF(C14="Must","Обязательно",IF(C14="Should","Желательно",IF(C14="Could","Возможно",IF(C14="Won't","Не в этот раз",""))))</f>
         <v/>
       </c>
-      <c r="E14" s="251" t="inlineStr">
+      <c r="E14" s="247" t="inlineStr">
         <is>
           <t>Удобно, но не критично</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="247" t="inlineStr">
+    <row r="15" ht="27.6" customHeight="1">
+      <c r="A15" s="243" t="inlineStr">
         <is>
           <t>MS-11</t>
         </is>
       </c>
-      <c r="B15" s="248" t="inlineStr">
+      <c r="B15" s="244" t="inlineStr">
         <is>
           <t>Программа лояльности / бонусы</t>
         </is>
       </c>
-      <c r="C15" s="249" t="inlineStr">
+      <c r="C15" s="245" t="inlineStr">
         <is>
           <t>Won't</t>
         </is>
       </c>
-      <c r="D15" s="250">
+      <c r="D15" s="246">
         <f>IF(C15="Must","Обязательно",IF(C15="Should","Желательно",IF(C15="Could","Возможно",IF(C15="Won't","Не в этот раз",""))))</f>
         <v/>
       </c>
-      <c r="E15" s="251" t="inlineStr">
+      <c r="E15" s="247" t="inlineStr">
         <is>
           <t>Отдельная инициатива на следующий квартал</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="247" t="inlineStr">
+      <c r="A16" s="243" t="inlineStr">
         <is>
           <t>MS-12</t>
         </is>
       </c>
-      <c r="B16" s="248" t="inlineStr">
+      <c r="B16" s="244" t="inlineStr">
         <is>
           <t>Офлайн-режим приложения</t>
         </is>
       </c>
-      <c r="C16" s="249" t="inlineStr">
+      <c r="C16" s="245" t="inlineStr">
         <is>
           <t>Won't</t>
         </is>
       </c>
-      <c r="D16" s="250">
+      <c r="D16" s="246">
         <f>IF(C16="Must","Обязательно",IF(C16="Should","Желательно",IF(C16="Could","Возможно",IF(C16="Won't","Не в этот раз",""))))</f>
         <v/>
       </c>
-      <c r="E16" s="251" t="inlineStr">
+      <c r="E16" s="247" t="inlineStr">
         <is>
           <t>Вне scope текущего релиза</t>
         </is>
@@ -49616,57 +50092,57 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="252" t="inlineStr">
+      <c r="A19" s="248" t="inlineStr">
         <is>
           <t>Категория</t>
         </is>
       </c>
-      <c r="B19" s="252" t="inlineStr">
+      <c r="B19" s="248" t="inlineStr">
         <is>
           <t>Кол-во</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="253" t="inlineStr">
+      <c r="A20" s="249" t="inlineStr">
         <is>
           <t>Must</t>
         </is>
       </c>
-      <c r="B20" s="250">
+      <c r="B20" s="246">
         <f>COUNTIF($C$5:$C$16,"Must")</f>
         <v/>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="254" t="inlineStr">
+      <c r="A21" s="250" t="inlineStr">
         <is>
           <t>Should</t>
         </is>
       </c>
-      <c r="B21" s="250">
+      <c r="B21" s="246">
         <f>COUNTIF($C$5:$C$16,"Should")</f>
         <v/>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="255" t="inlineStr">
+      <c r="A22" s="251" t="inlineStr">
         <is>
           <t>Could</t>
         </is>
       </c>
-      <c r="B22" s="250">
+      <c r="B22" s="246">
         <f>COUNTIF($C$5:$C$16,"Could")</f>
         <v/>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="256" t="inlineStr">
+      <c r="A23" s="252" t="inlineStr">
         <is>
           <t>Won't</t>
         </is>
       </c>
-      <c r="B23" s="250">
+      <c r="B23" s="246">
         <f>COUNTIF($C$5:$C$16,"Won't")</f>
         <v/>
       </c>
@@ -49740,16 +50216,16 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="C5:C16">
-    <cfRule type="cellIs" priority="1" operator="equal" dxfId="47">
+    <cfRule type="cellIs" priority="1" operator="equal" dxfId="26">
       <formula>"Must"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="2" operator="equal" dxfId="48">
+    <cfRule type="cellIs" priority="2" operator="equal" dxfId="25">
       <formula>"Should"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="3" operator="equal" dxfId="49">
+    <cfRule type="cellIs" priority="3" operator="equal" dxfId="24">
       <formula>"Could"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="4" operator="equal" dxfId="50">
+    <cfRule type="cellIs" priority="4" operator="equal" dxfId="23">
       <formula>"Won't"</formula>
     </cfRule>
   </conditionalFormatting>

--- a/Планирование_спринта_PRO.xlsx
+++ b/Планирование_спринта_PRO.xlsx
@@ -38,6 +38,11 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Распределение" sheetId="30" state="visible" r:id="rId30"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Time to Market" sheetId="31" state="visible" r:id="rId31"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FAQ" sheetId="32" state="visible" r:id="rId32"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Груминг" sheetId="33" state="visible" r:id="rId33"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Демо спринта" sheetId="34" state="visible" r:id="rId34"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Дэйли" sheetId="35" state="visible" r:id="rId35"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="График отпусков" sheetId="36" state="visible" r:id="rId36"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Дни рождения" sheetId="37" state="visible" r:id="rId37"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
@@ -47050,6 +47055,1168 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet33.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="9" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="34" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="11" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="213" t="inlineStr">
+        <is>
+          <t>Груминг бэклога (Backlog Refinement)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="225" t="inlineStr">
+        <is>
+          <t>Подготовка элементов бэклога к спринту: оценка, декомпозиция, уточнение, приоритизация.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="256" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B4" s="256" t="inlineStr">
+        <is>
+          <t>Дата</t>
+        </is>
+      </c>
+      <c r="C4" s="256" t="inlineStr">
+        <is>
+          <t>Элемент бэклога</t>
+        </is>
+      </c>
+      <c r="D4" s="256" t="inlineStr">
+        <is>
+          <t>Действие</t>
+        </is>
+      </c>
+      <c r="E4" s="256" t="inlineStr">
+        <is>
+          <t>Оценка (SP)</t>
+        </is>
+      </c>
+      <c r="F4" s="256" t="inlineStr">
+        <is>
+          <t>Готовность</t>
+        </is>
+      </c>
+      <c r="G4" s="256" t="inlineStr">
+        <is>
+          <t>Ответственный</t>
+        </is>
+      </c>
+      <c r="H4" s="256" t="inlineStr">
+        <is>
+          <t>Комментарий</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="30" customHeight="1">
+      <c r="A5" s="260" t="inlineStr">
+        <is>
+          <t>GR-01</t>
+        </is>
+      </c>
+      <c r="B5" s="260" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="C5" s="260" t="inlineStr">
+        <is>
+          <t>История: оформление заказа</t>
+        </is>
+      </c>
+      <c r="D5" s="260" t="inlineStr">
+        <is>
+          <t>Декомпозиция</t>
+        </is>
+      </c>
+      <c r="E5" s="260" t="n">
+        <v>8</v>
+      </c>
+      <c r="F5" s="260" t="inlineStr">
+        <is>
+          <t>Готово к спринту</t>
+        </is>
+      </c>
+      <c r="G5" s="260" t="inlineStr">
+        <is>
+          <t>Иванов А.</t>
+        </is>
+      </c>
+      <c r="H5" s="260" t="inlineStr">
+        <is>
+          <t>Разбита на 3 подзадачи; критерии приёмки уточнены</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="30" customHeight="1">
+      <c r="A6" s="260" t="inlineStr">
+        <is>
+          <t>GR-02</t>
+        </is>
+      </c>
+      <c r="B6" s="260" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="C6" s="260" t="inlineStr">
+        <is>
+          <t>История: оплата картой</t>
+        </is>
+      </c>
+      <c r="D6" s="260" t="inlineStr">
+        <is>
+          <t>Оценка</t>
+        </is>
+      </c>
+      <c r="E6" s="260" t="n">
+        <v>5</v>
+      </c>
+      <c r="F6" s="260" t="inlineStr">
+        <is>
+          <t>Готово к спринту</t>
+        </is>
+      </c>
+      <c r="G6" s="260" t="inlineStr">
+        <is>
+          <t>Кузнецов Д.</t>
+        </is>
+      </c>
+      <c r="H6" s="260" t="inlineStr">
+        <is>
+          <t>Оценка по покеру, риск интеграции учтён</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="30" customHeight="1">
+      <c r="A7" s="260" t="inlineStr">
+        <is>
+          <t>GR-03</t>
+        </is>
+      </c>
+      <c r="B7" s="260" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="C7" s="260" t="inlineStr">
+        <is>
+          <t>История: промокоды</t>
+        </is>
+      </c>
+      <c r="D7" s="260" t="inlineStr">
+        <is>
+          <t>Уточнение</t>
+        </is>
+      </c>
+      <c r="E7" s="260" t="n">
+        <v>3</v>
+      </c>
+      <c r="F7" s="260" t="inlineStr">
+        <is>
+          <t>Требует доработки</t>
+        </is>
+      </c>
+      <c r="G7" s="260" t="inlineStr">
+        <is>
+          <t>Петрова М.</t>
+        </is>
+      </c>
+      <c r="H7" s="260" t="inlineStr">
+        <is>
+          <t>Нужны правила комбинирования скидок от заказчика</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="30" customHeight="1">
+      <c r="A8" s="260" t="inlineStr">
+        <is>
+          <t>GR-04</t>
+        </is>
+      </c>
+      <c r="B8" s="260" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="C8" s="260" t="inlineStr">
+        <is>
+          <t>Фича: рекомендации товаров</t>
+        </is>
+      </c>
+      <c r="D8" s="260" t="inlineStr">
+        <is>
+          <t>Приоритизация</t>
+        </is>
+      </c>
+      <c r="E8" s="260" t="n">
+        <v>13</v>
+      </c>
+      <c r="F8" s="260" t="inlineStr">
+        <is>
+          <t>Требует доработки</t>
+        </is>
+      </c>
+      <c r="G8" s="260" t="inlineStr">
+        <is>
+          <t>Орлова Е.</t>
+        </is>
+      </c>
+      <c r="H8" s="260" t="inlineStr">
+        <is>
+          <t>Отложено: зависит от аналитики поведения</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="30" customHeight="1">
+      <c r="A9" s="260" t="inlineStr">
+        <is>
+          <t>GR-05</t>
+        </is>
+      </c>
+      <c r="B9" s="260" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="C9" s="260" t="inlineStr">
+        <is>
+          <t>История: история заказов</t>
+        </is>
+      </c>
+      <c r="D9" s="260" t="inlineStr">
+        <is>
+          <t>Оценка</t>
+        </is>
+      </c>
+      <c r="E9" s="260" t="n">
+        <v>5</v>
+      </c>
+      <c r="F9" s="260" t="inlineStr">
+        <is>
+          <t>Готово к спринту</t>
+        </is>
+      </c>
+      <c r="G9" s="260" t="inlineStr">
+        <is>
+          <t>Соколов Р.</t>
+        </is>
+      </c>
+      <c r="H9" s="260" t="inlineStr">
+        <is>
+          <t>Готова к взятию в спринт 4</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet34.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="9" customWidth="1" min="1" max="1"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="32" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="34" customWidth="1" min="7" max="7"/>
+    <col width="15" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="213" t="inlineStr">
+        <is>
+          <t>Демо спринта (Sprint Review)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="225" t="inlineStr">
+        <is>
+          <t>Демонстрация инкремента заказчикам, обратная связь и решение о приёмке.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="256" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B4" s="256" t="inlineStr">
+        <is>
+          <t>Спринт</t>
+        </is>
+      </c>
+      <c r="C4" s="256" t="inlineStr">
+        <is>
+          <t>Дата</t>
+        </is>
+      </c>
+      <c r="D4" s="256" t="inlineStr">
+        <is>
+          <t>Что демонстрировали</t>
+        </is>
+      </c>
+      <c r="E4" s="256" t="inlineStr">
+        <is>
+          <t>Докладчик</t>
+        </is>
+      </c>
+      <c r="F4" s="256" t="inlineStr">
+        <is>
+          <t>Участники</t>
+        </is>
+      </c>
+      <c r="G4" s="256" t="inlineStr">
+        <is>
+          <t>Обратная связь</t>
+        </is>
+      </c>
+      <c r="H4" s="256" t="inlineStr">
+        <is>
+          <t>Итог</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="30" customHeight="1">
+      <c r="A5" s="260" t="inlineStr">
+        <is>
+          <t>DM-01</t>
+        </is>
+      </c>
+      <c r="B5" s="260" t="n">
+        <v>1</v>
+      </c>
+      <c r="C5" s="260" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="D5" s="260" t="inlineStr">
+        <is>
+          <t>Каркас каталога и карточка товара</t>
+        </is>
+      </c>
+      <c r="E5" s="260" t="inlineStr">
+        <is>
+          <t>Иванов А.</t>
+        </is>
+      </c>
+      <c r="F5" s="260" t="inlineStr">
+        <is>
+          <t>PO, маркетинг</t>
+        </is>
+      </c>
+      <c r="G5" s="260" t="inlineStr">
+        <is>
+          <t>Одобрено; просят добавить бейджи скидок</t>
+        </is>
+      </c>
+      <c r="H5" s="260" t="inlineStr">
+        <is>
+          <t>Принято</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="30" customHeight="1">
+      <c r="A6" s="260" t="inlineStr">
+        <is>
+          <t>DM-02</t>
+        </is>
+      </c>
+      <c r="B6" s="260" t="n">
+        <v>2</v>
+      </c>
+      <c r="C6" s="260" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="D6" s="260" t="inlineStr">
+        <is>
+          <t>Корзина и черновик оформления заказа</t>
+        </is>
+      </c>
+      <c r="E6" s="260" t="inlineStr">
+        <is>
+          <t>Петрова М.</t>
+        </is>
+      </c>
+      <c r="F6" s="260" t="inlineStr">
+        <is>
+          <t>PO, поддержка</t>
+        </is>
+      </c>
+      <c r="G6" s="260" t="inlineStr">
+        <is>
+          <t>В целом ок; доработать валидацию адреса</t>
+        </is>
+      </c>
+      <c r="H6" s="260" t="inlineStr">
+        <is>
+          <t>На доработку</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="30" customHeight="1">
+      <c r="A7" s="260" t="inlineStr">
+        <is>
+          <t>DM-03</t>
+        </is>
+      </c>
+      <c r="B7" s="260" t="n">
+        <v>3</v>
+      </c>
+      <c r="C7" s="260" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="D7" s="260" t="inlineStr">
+        <is>
+          <t>Оплата картой (MVP)</t>
+        </is>
+      </c>
+      <c r="E7" s="260" t="inlineStr">
+        <is>
+          <t>Кузнецов Д.</t>
+        </is>
+      </c>
+      <c r="F7" s="260" t="inlineStr">
+        <is>
+          <t>PO, финансы, безопасность</t>
+        </is>
+      </c>
+      <c r="G7" s="260" t="inlineStr">
+        <is>
+          <t>Принято для пилота; нужен лог транзакций</t>
+        </is>
+      </c>
+      <c r="H7" s="260" t="inlineStr">
+        <is>
+          <t>Принято</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet35.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="9" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="8" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="32" customWidth="1" min="5" max="5"/>
+    <col width="32" customWidth="1" min="6" max="6"/>
+    <col width="30" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="213" t="inlineStr">
+        <is>
+          <t>Дэйли (Daily Standup)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="225" t="inlineStr">
+        <is>
+          <t>Ежедневная синхронизация команды: вчера / сегодня / блокеры — по дням и участникам.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="256" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B4" s="256" t="inlineStr">
+        <is>
+          <t>Дата</t>
+        </is>
+      </c>
+      <c r="C4" s="256" t="inlineStr">
+        <is>
+          <t>Спринт</t>
+        </is>
+      </c>
+      <c r="D4" s="256" t="inlineStr">
+        <is>
+          <t>Участник</t>
+        </is>
+      </c>
+      <c r="E4" s="256" t="inlineStr">
+        <is>
+          <t>Вчера</t>
+        </is>
+      </c>
+      <c r="F4" s="256" t="inlineStr">
+        <is>
+          <t>Сегодня</t>
+        </is>
+      </c>
+      <c r="G4" s="256" t="inlineStr">
+        <is>
+          <t>Блокер</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="30" customHeight="1">
+      <c r="A5" s="260" t="inlineStr">
+        <is>
+          <t>DL-01</t>
+        </is>
+      </c>
+      <c r="B5" s="260" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="C5" s="260" t="n">
+        <v>3</v>
+      </c>
+      <c r="D5" s="260" t="inlineStr">
+        <is>
+          <t>Иванов А.</t>
+        </is>
+      </c>
+      <c r="E5" s="260" t="inlineStr">
+        <is>
+          <t>Завершил API оформления заказа</t>
+        </is>
+      </c>
+      <c r="F5" s="260" t="inlineStr">
+        <is>
+          <t>Ревью и интеграция оплаты</t>
+        </is>
+      </c>
+      <c r="G5" s="260" t="inlineStr"/>
+    </row>
+    <row r="6" ht="30" customHeight="1">
+      <c r="A6" s="260" t="inlineStr">
+        <is>
+          <t>DL-02</t>
+        </is>
+      </c>
+      <c r="B6" s="260" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="C6" s="260" t="n">
+        <v>3</v>
+      </c>
+      <c r="D6" s="260" t="inlineStr">
+        <is>
+          <t>Кузнецов Д.</t>
+        </is>
+      </c>
+      <c r="E6" s="260" t="inlineStr">
+        <is>
+          <t>Настроил песочницу платёжного шлюза</t>
+        </is>
+      </c>
+      <c r="F6" s="260" t="inlineStr">
+        <is>
+          <t>Обработка вебхуков оплаты</t>
+        </is>
+      </c>
+      <c r="G6" s="260" t="inlineStr">
+        <is>
+          <t>Ждём ключи от платёжного провайдера</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="30" customHeight="1">
+      <c r="A7" s="260" t="inlineStr">
+        <is>
+          <t>DL-03</t>
+        </is>
+      </c>
+      <c r="B7" s="260" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="C7" s="260" t="n">
+        <v>3</v>
+      </c>
+      <c r="D7" s="260" t="inlineStr">
+        <is>
+          <t>Петрова М.</t>
+        </is>
+      </c>
+      <c r="E7" s="260" t="inlineStr">
+        <is>
+          <t>Вёрстка корзины</t>
+        </is>
+      </c>
+      <c r="F7" s="260" t="inlineStr">
+        <is>
+          <t>Валидация адреса доставки</t>
+        </is>
+      </c>
+      <c r="G7" s="260" t="inlineStr"/>
+    </row>
+    <row r="8" ht="30" customHeight="1">
+      <c r="A8" s="260" t="inlineStr">
+        <is>
+          <t>DL-04</t>
+        </is>
+      </c>
+      <c r="B8" s="260" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="C8" s="260" t="n">
+        <v>3</v>
+      </c>
+      <c r="D8" s="260" t="inlineStr">
+        <is>
+          <t>Иванов А.</t>
+        </is>
+      </c>
+      <c r="E8" s="260" t="inlineStr">
+        <is>
+          <t>Интеграция оплаты</t>
+        </is>
+      </c>
+      <c r="F8" s="260" t="inlineStr">
+        <is>
+          <t>Логирование транзакций</t>
+        </is>
+      </c>
+      <c r="G8" s="260" t="inlineStr"/>
+    </row>
+    <row r="9" ht="30" customHeight="1">
+      <c r="A9" s="260" t="inlineStr">
+        <is>
+          <t>DL-05</t>
+        </is>
+      </c>
+      <c r="B9" s="260" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="C9" s="260" t="n">
+        <v>3</v>
+      </c>
+      <c r="D9" s="260" t="inlineStr">
+        <is>
+          <t>Соколов Р.</t>
+        </is>
+      </c>
+      <c r="E9" s="260" t="inlineStr">
+        <is>
+          <t>Тест-кейсы оформления</t>
+        </is>
+      </c>
+      <c r="F9" s="260" t="inlineStr">
+        <is>
+          <t>Регресс по корзине</t>
+        </is>
+      </c>
+      <c r="G9" s="260" t="inlineStr">
+        <is>
+          <t>Нестабильный стенд QA</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet36.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="9" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="8" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="34" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="213" t="inlineStr">
+        <is>
+          <t>График отпусков и отсутствий</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="225" t="inlineStr">
+        <is>
+          <t>Отпуска, больничные, отгулы и командировки — для учёта доступности команды.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="256" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B4" s="256" t="inlineStr">
+        <is>
+          <t>Участник</t>
+        </is>
+      </c>
+      <c r="C4" s="256" t="inlineStr">
+        <is>
+          <t>Тип</t>
+        </is>
+      </c>
+      <c r="D4" s="256" t="inlineStr">
+        <is>
+          <t>С</t>
+        </is>
+      </c>
+      <c r="E4" s="256" t="inlineStr">
+        <is>
+          <t>По</t>
+        </is>
+      </c>
+      <c r="F4" s="256" t="inlineStr">
+        <is>
+          <t>Дней</t>
+        </is>
+      </c>
+      <c r="G4" s="256" t="inlineStr">
+        <is>
+          <t>Статус</t>
+        </is>
+      </c>
+      <c r="H4" s="256" t="inlineStr">
+        <is>
+          <t>Комментарий</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="30" customHeight="1">
+      <c r="A5" s="260" t="inlineStr">
+        <is>
+          <t>VC-01</t>
+        </is>
+      </c>
+      <c r="B5" s="260" t="inlineStr">
+        <is>
+          <t>Иванов А.</t>
+        </is>
+      </c>
+      <c r="C5" s="260" t="inlineStr">
+        <is>
+          <t>Отпуск</t>
+        </is>
+      </c>
+      <c r="D5" s="260" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="E5" s="260" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="F5" s="260" t="n">
+        <v>10</v>
+      </c>
+      <c r="G5" s="260" t="inlineStr">
+        <is>
+          <t>Утверждён</t>
+        </is>
+      </c>
+      <c r="H5" s="260" t="inlineStr">
+        <is>
+          <t>Плановый отпуск</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="30" customHeight="1">
+      <c r="A6" s="260" t="inlineStr">
+        <is>
+          <t>VC-02</t>
+        </is>
+      </c>
+      <c r="B6" s="260" t="inlineStr">
+        <is>
+          <t>Петрова М.</t>
+        </is>
+      </c>
+      <c r="C6" s="260" t="inlineStr">
+        <is>
+          <t>Отгул</t>
+        </is>
+      </c>
+      <c r="D6" s="260" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="E6" s="260" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="F6" s="260" t="n">
+        <v>1</v>
+      </c>
+      <c r="G6" s="260" t="inlineStr">
+        <is>
+          <t>Утверждён</t>
+        </is>
+      </c>
+      <c r="H6" s="260" t="inlineStr"/>
+    </row>
+    <row r="7" ht="30" customHeight="1">
+      <c r="A7" s="260" t="inlineStr">
+        <is>
+          <t>VC-03</t>
+        </is>
+      </c>
+      <c r="B7" s="260" t="inlineStr">
+        <is>
+          <t>Кузнецов Д.</t>
+        </is>
+      </c>
+      <c r="C7" s="260" t="inlineStr">
+        <is>
+          <t>Командировка</t>
+        </is>
+      </c>
+      <c r="D7" s="260" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="E7" s="260" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="F7" s="260" t="n">
+        <v>3</v>
+      </c>
+      <c r="G7" s="260" t="inlineStr">
+        <is>
+          <t>Запланирован</t>
+        </is>
+      </c>
+      <c r="H7" s="260" t="inlineStr">
+        <is>
+          <t>Встреча с платёжным провайдером</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="30" customHeight="1">
+      <c r="A8" s="260" t="inlineStr">
+        <is>
+          <t>VC-04</t>
+        </is>
+      </c>
+      <c r="B8" s="260" t="inlineStr">
+        <is>
+          <t>Орлова Е.</t>
+        </is>
+      </c>
+      <c r="C8" s="260" t="inlineStr">
+        <is>
+          <t>Больничный</t>
+        </is>
+      </c>
+      <c r="D8" s="260" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="E8" s="260" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="F8" s="260" t="n">
+        <v>3</v>
+      </c>
+      <c r="G8" s="260" t="inlineStr">
+        <is>
+          <t>Завершён</t>
+        </is>
+      </c>
+      <c r="H8" s="260" t="inlineStr"/>
+    </row>
+    <row r="9" ht="30" customHeight="1">
+      <c r="A9" s="260" t="inlineStr">
+        <is>
+          <t>VC-05</t>
+        </is>
+      </c>
+      <c r="B9" s="260" t="inlineStr">
+        <is>
+          <t>Соколов Р.</t>
+        </is>
+      </c>
+      <c r="C9" s="260" t="inlineStr">
+        <is>
+          <t>Отпуск</t>
+        </is>
+      </c>
+      <c r="D9" s="260" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="E9" s="260" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="F9" s="260" t="n">
+        <v>10</v>
+      </c>
+      <c r="G9" s="260" t="inlineStr">
+        <is>
+          <t>Запланирован</t>
+        </is>
+      </c>
+      <c r="H9" s="260" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet37.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="9" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="34" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="213" t="inlineStr">
+        <is>
+          <t>Дни рождения команды</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="225" t="inlineStr">
+        <is>
+          <t>Даты рождения участников; в приложении показываются ближайшие даты с обратным отсчётом.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="256" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B4" s="256" t="inlineStr">
+        <is>
+          <t>Участник</t>
+        </is>
+      </c>
+      <c r="C4" s="256" t="inlineStr">
+        <is>
+          <t>Дата рождения</t>
+        </is>
+      </c>
+      <c r="D4" s="256" t="inlineStr">
+        <is>
+          <t>Роль</t>
+        </is>
+      </c>
+      <c r="E4" s="256" t="inlineStr">
+        <is>
+          <t>Комментарий</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="30" customHeight="1">
+      <c r="A5" s="260" t="inlineStr">
+        <is>
+          <t>BD-01</t>
+        </is>
+      </c>
+      <c r="B5" s="260" t="inlineStr">
+        <is>
+          <t>Иванов А.</t>
+        </is>
+      </c>
+      <c r="C5" s="260" t="inlineStr">
+        <is>
+          <t>1990-09-20</t>
+        </is>
+      </c>
+      <c r="D5" s="260" t="inlineStr">
+        <is>
+          <t>Backend</t>
+        </is>
+      </c>
+      <c r="E5" s="260" t="inlineStr"/>
+    </row>
+    <row r="6" ht="30" customHeight="1">
+      <c r="A6" s="260" t="inlineStr">
+        <is>
+          <t>BD-02</t>
+        </is>
+      </c>
+      <c r="B6" s="260" t="inlineStr">
+        <is>
+          <t>Петрова М.</t>
+        </is>
+      </c>
+      <c r="C6" s="260" t="inlineStr">
+        <is>
+          <t>1993-10-05</t>
+        </is>
+      </c>
+      <c r="D6" s="260" t="inlineStr">
+        <is>
+          <t>Frontend</t>
+        </is>
+      </c>
+      <c r="E6" s="260" t="inlineStr"/>
+    </row>
+    <row r="7" ht="30" customHeight="1">
+      <c r="A7" s="260" t="inlineStr">
+        <is>
+          <t>BD-03</t>
+        </is>
+      </c>
+      <c r="B7" s="260" t="inlineStr">
+        <is>
+          <t>Кузнецов Д.</t>
+        </is>
+      </c>
+      <c r="C7" s="260" t="inlineStr">
+        <is>
+          <t>1988-11-12</t>
+        </is>
+      </c>
+      <c r="D7" s="260" t="inlineStr">
+        <is>
+          <t>Backend</t>
+        </is>
+      </c>
+      <c r="E7" s="260" t="inlineStr"/>
+    </row>
+    <row r="8" ht="30" customHeight="1">
+      <c r="A8" s="260" t="inlineStr">
+        <is>
+          <t>BD-04</t>
+        </is>
+      </c>
+      <c r="B8" s="260" t="inlineStr">
+        <is>
+          <t>Орлова Е.</t>
+        </is>
+      </c>
+      <c r="C8" s="260" t="inlineStr">
+        <is>
+          <t>1995-09-28</t>
+        </is>
+      </c>
+      <c r="D8" s="260" t="inlineStr">
+        <is>
+          <t>Analyst</t>
+        </is>
+      </c>
+      <c r="E8" s="260" t="inlineStr"/>
+    </row>
+    <row r="9" ht="30" customHeight="1">
+      <c r="A9" s="260" t="inlineStr">
+        <is>
+          <t>BD-05</t>
+        </is>
+      </c>
+      <c r="B9" s="260" t="inlineStr">
+        <is>
+          <t>Соколов Р.</t>
+        </is>
+      </c>
+      <c r="C9" s="260" t="inlineStr">
+        <is>
+          <t>1991-12-03</t>
+        </is>
+      </c>
+      <c r="D9" s="260" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="E9" s="260" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/Планирование_спринта_PRO.xlsx
+++ b/Планирование_спринта_PRO.xlsx
@@ -43,6 +43,10 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Дэйли" sheetId="35" state="visible" r:id="rId35"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="График отпусков" sheetId="36" state="visible" r:id="rId36"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Дни рождения" sheetId="37" state="visible" r:id="rId37"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Настроение" sheetId="38" state="visible" r:id="rId38"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Kudos" sheetId="39" state="visible" r:id="rId39"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Эксперименты" sheetId="40" state="visible" r:id="rId40"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Team Radar" sheetId="41" state="visible" r:id="rId41"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
@@ -48217,6 +48221,253 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet38.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="9" customWidth="1" min="1" max="1"/>
+    <col width="9" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="44" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="213" t="inlineStr">
+        <is>
+          <t>Настроение команды по спринтам</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="225" t="inlineStr">
+        <is>
+          <t>Оценка климата спринта (1–5) — в приложении показывается трендом.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="256" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B4" s="256" t="inlineStr">
+        <is>
+          <t>Спринт</t>
+        </is>
+      </c>
+      <c r="C4" s="256" t="inlineStr">
+        <is>
+          <t>Настроение (1–5)</t>
+        </is>
+      </c>
+      <c r="D4" s="256" t="inlineStr">
+        <is>
+          <t>Комментарий</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="28" customHeight="1">
+      <c r="A5" s="260" t="inlineStr">
+        <is>
+          <t>MD-01</t>
+        </is>
+      </c>
+      <c r="B5" s="260" t="n">
+        <v>1</v>
+      </c>
+      <c r="C5" s="260" t="n">
+        <v>4</v>
+      </c>
+      <c r="D5" s="260" t="inlineStr">
+        <is>
+          <t>Хороший старт, понятные цели</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="28" customHeight="1">
+      <c r="A6" s="260" t="inlineStr">
+        <is>
+          <t>MD-02</t>
+        </is>
+      </c>
+      <c r="B6" s="260" t="n">
+        <v>2</v>
+      </c>
+      <c r="C6" s="260" t="n">
+        <v>3</v>
+      </c>
+      <c r="D6" s="260" t="inlineStr">
+        <is>
+          <t>Много переключений между задачами</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="28" customHeight="1">
+      <c r="A7" s="260" t="inlineStr">
+        <is>
+          <t>MD-03</t>
+        </is>
+      </c>
+      <c r="B7" s="260" t="n">
+        <v>3</v>
+      </c>
+      <c r="C7" s="260" t="n">
+        <v>4</v>
+      </c>
+      <c r="D7" s="260" t="inlineStr">
+        <is>
+          <t>Наладили процесс, меньше блокеров</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet39.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="9" customWidth="1" min="1" max="1"/>
+    <col width="9" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="44" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="213" t="inlineStr">
+        <is>
+          <t>Kudos — благодарности</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="225" t="inlineStr">
+        <is>
+          <t>Публичное признание вклада коллег на ретроспективе.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="256" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B4" s="256" t="inlineStr">
+        <is>
+          <t>Спринт</t>
+        </is>
+      </c>
+      <c r="C4" s="256" t="inlineStr">
+        <is>
+          <t>От кого</t>
+        </is>
+      </c>
+      <c r="D4" s="256" t="inlineStr">
+        <is>
+          <t>Кому</t>
+        </is>
+      </c>
+      <c r="E4" s="256" t="inlineStr">
+        <is>
+          <t>За что</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="28" customHeight="1">
+      <c r="A5" s="260" t="inlineStr">
+        <is>
+          <t>KD-01</t>
+        </is>
+      </c>
+      <c r="B5" s="260" t="n">
+        <v>3</v>
+      </c>
+      <c r="C5" s="260" t="inlineStr">
+        <is>
+          <t>Команда</t>
+        </is>
+      </c>
+      <c r="D5" s="260" t="inlineStr">
+        <is>
+          <t>Кузнецов Д.</t>
+        </is>
+      </c>
+      <c r="E5" s="260" t="inlineStr">
+        <is>
+          <t>Быстро поднял платёжную интеграцию</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="28" customHeight="1">
+      <c r="A6" s="260" t="inlineStr">
+        <is>
+          <t>KD-02</t>
+        </is>
+      </c>
+      <c r="B6" s="260" t="n">
+        <v>3</v>
+      </c>
+      <c r="C6" s="260" t="inlineStr">
+        <is>
+          <t>Петрова М.</t>
+        </is>
+      </c>
+      <c r="D6" s="260" t="inlineStr">
+        <is>
+          <t>Соколов Р.</t>
+        </is>
+      </c>
+      <c r="E6" s="260" t="inlineStr">
+        <is>
+          <t>Помог с регрессом в выходной</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="28" customHeight="1">
+      <c r="A7" s="260" t="inlineStr">
+        <is>
+          <t>KD-03</t>
+        </is>
+      </c>
+      <c r="B7" s="260" t="n">
+        <v>2</v>
+      </c>
+      <c r="C7" s="260" t="inlineStr">
+        <is>
+          <t>PO</t>
+        </is>
+      </c>
+      <c r="D7" s="260" t="inlineStr">
+        <is>
+          <t>Команда</t>
+        </is>
+      </c>
+      <c r="E7" s="260" t="inlineStr">
+        <is>
+          <t>Отличное демо корзины</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
@@ -50094,6 +50345,296 @@
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet40.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="9" customWidth="1" min="1" max="1"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="28" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="213" t="inlineStr">
+        <is>
+          <t>Эксперименты — проверяемые улучшения</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="225" t="inlineStr">
+        <is>
+          <t>Гипотеза → действие → метрика → результат.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="256" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B4" s="256" t="inlineStr">
+        <is>
+          <t>Спринт</t>
+        </is>
+      </c>
+      <c r="C4" s="256" t="inlineStr">
+        <is>
+          <t>Гипотеза</t>
+        </is>
+      </c>
+      <c r="D4" s="256" t="inlineStr">
+        <is>
+          <t>Действие</t>
+        </is>
+      </c>
+      <c r="E4" s="256" t="inlineStr">
+        <is>
+          <t>Метрика</t>
+        </is>
+      </c>
+      <c r="F4" s="256" t="inlineStr">
+        <is>
+          <t>Результат</t>
+        </is>
+      </c>
+      <c r="G4" s="256" t="inlineStr">
+        <is>
+          <t>Статус</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="28" customHeight="1">
+      <c r="A5" s="260" t="inlineStr">
+        <is>
+          <t>EX-01</t>
+        </is>
+      </c>
+      <c r="B5" s="260" t="n">
+        <v>2</v>
+      </c>
+      <c r="C5" s="260" t="inlineStr">
+        <is>
+          <t>Парное ревью ускорит закрытие сложных задач</t>
+        </is>
+      </c>
+      <c r="D5" s="260" t="inlineStr">
+        <is>
+          <t>Ввести парное ревью для сложных PR</t>
+        </is>
+      </c>
+      <c r="E5" s="260" t="inlineStr">
+        <is>
+          <t>Cycle time сложных задач</t>
+        </is>
+      </c>
+      <c r="F5" s="260" t="inlineStr">
+        <is>
+          <t>Cycle time −15%</t>
+        </is>
+      </c>
+      <c r="G5" s="260" t="inlineStr">
+        <is>
+          <t>Успешно</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="28" customHeight="1">
+      <c r="A6" s="260" t="inlineStr">
+        <is>
+          <t>EX-02</t>
+        </is>
+      </c>
+      <c r="B6" s="260" t="n">
+        <v>3</v>
+      </c>
+      <c r="C6" s="260" t="inlineStr">
+        <is>
+          <t>WIP-лимит снизит переключения и ускорит поток</t>
+        </is>
+      </c>
+      <c r="D6" s="260" t="inlineStr">
+        <is>
+          <t>Лимит 2 задачи «В работе» на человека</t>
+        </is>
+      </c>
+      <c r="E6" s="260" t="inlineStr">
+        <is>
+          <t>Число параллельных задач</t>
+        </is>
+      </c>
+      <c r="F6" s="260" t="inlineStr">
+        <is>
+          <t>В процессе замера</t>
+        </is>
+      </c>
+      <c r="G6" s="260" t="inlineStr">
+        <is>
+          <t>Идёт</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet41.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="9" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="213" t="inlineStr">
+        <is>
+          <t>Team Radar — самооценка команды</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="225" t="inlineStr">
+        <is>
+          <t>Оценка по осям 1–5: текущий и прошлый спринт.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="256" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B4" s="256" t="inlineStr">
+        <is>
+          <t>Ось</t>
+        </is>
+      </c>
+      <c r="C4" s="256" t="inlineStr">
+        <is>
+          <t>Сейчас (1–5)</t>
+        </is>
+      </c>
+      <c r="D4" s="256" t="inlineStr">
+        <is>
+          <t>Прошлый (1–5)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="28" customHeight="1">
+      <c r="A5" s="260" t="inlineStr">
+        <is>
+          <t>RD-01</t>
+        </is>
+      </c>
+      <c r="B5" s="260" t="inlineStr">
+        <is>
+          <t>Коммуникация</t>
+        </is>
+      </c>
+      <c r="C5" s="260" t="n">
+        <v>4</v>
+      </c>
+      <c r="D5" s="260" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6" ht="28" customHeight="1">
+      <c r="A6" s="260" t="inlineStr">
+        <is>
+          <t>RD-02</t>
+        </is>
+      </c>
+      <c r="B6" s="260" t="inlineStr">
+        <is>
+          <t>Качество</t>
+        </is>
+      </c>
+      <c r="C6" s="260" t="n">
+        <v>3</v>
+      </c>
+      <c r="D6" s="260" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="7" ht="28" customHeight="1">
+      <c r="A7" s="260" t="inlineStr">
+        <is>
+          <t>RD-03</t>
+        </is>
+      </c>
+      <c r="B7" s="260" t="inlineStr">
+        <is>
+          <t>Процесс</t>
+        </is>
+      </c>
+      <c r="C7" s="260" t="n">
+        <v>4</v>
+      </c>
+      <c r="D7" s="260" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="8" ht="28" customHeight="1">
+      <c r="A8" s="260" t="inlineStr">
+        <is>
+          <t>RD-04</t>
+        </is>
+      </c>
+      <c r="B8" s="260" t="inlineStr">
+        <is>
+          <t>Инструменты</t>
+        </is>
+      </c>
+      <c r="C8" s="260" t="n">
+        <v>4</v>
+      </c>
+      <c r="D8" s="260" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9" ht="28" customHeight="1">
+      <c r="A9" s="260" t="inlineStr">
+        <is>
+          <t>RD-05</t>
+        </is>
+      </c>
+      <c r="B9" s="260" t="inlineStr">
+        <is>
+          <t>Нагрузка</t>
+        </is>
+      </c>
+      <c r="C9" s="260" t="n">
+        <v>3</v>
+      </c>
+      <c r="D9" s="260" t="n">
+        <v>2</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 

--- a/Планирование_спринта_PRO.xlsx
+++ b/Планирование_спринта_PRO.xlsx
@@ -38,15 +38,15 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Распределение" sheetId="30" state="visible" r:id="rId30"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Time to Market" sheetId="31" state="visible" r:id="rId31"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FAQ" sheetId="32" state="visible" r:id="rId32"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Груминг" sheetId="33" state="visible" r:id="rId33"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Демо спринта" sheetId="34" state="visible" r:id="rId34"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Дэйли" sheetId="35" state="visible" r:id="rId35"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="График отпусков" sheetId="36" state="visible" r:id="rId36"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Дни рождения" sheetId="37" state="visible" r:id="rId37"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Настроение" sheetId="38" state="visible" r:id="rId38"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Kudos" sheetId="39" state="visible" r:id="rId39"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Эксперименты" sheetId="40" state="visible" r:id="rId40"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Team Radar" sheetId="41" state="visible" r:id="rId41"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Настроение" sheetId="33" state="visible" r:id="rId33"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Kudos" sheetId="34" state="visible" r:id="rId34"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Эксперименты" sheetId="35" state="visible" r:id="rId35"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Team Radar" sheetId="36" state="visible" r:id="rId36"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Груминг" sheetId="37" state="visible" r:id="rId37"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Демо спринта" sheetId="38" state="visible" r:id="rId38"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Дэйли" sheetId="39" state="visible" r:id="rId39"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="График отпусков" sheetId="40" state="visible" r:id="rId40"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Дни рождения" sheetId="41" state="visible" r:id="rId41"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
@@ -47065,30 +47065,26 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H9"/>
+  <dimension ref="A1:D7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="34" customWidth="1" min="3" max="3"/>
-    <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="11" customWidth="1" min="5" max="5"/>
-    <col width="20" customWidth="1" min="6" max="6"/>
-    <col width="16" customWidth="1" min="7" max="7"/>
-    <col width="40" customWidth="1" min="8" max="8"/>
+    <col width="9" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="44" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="213" t="inlineStr">
         <is>
-          <t>Груминг бэклога (Backlog Refinement)</t>
+          <t>Настроение команды по спринтам</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="225" t="inlineStr">
         <is>
-          <t>Подготовка элементов бэклога к спринту: оценка, декомпозиция, уточнение, приоритизация.</t>
+          <t>Оценка климата спринта (1–5) — в приложении показывается трендом.</t>
         </is>
       </c>
     </row>
@@ -47100,237 +47096,71 @@
       </c>
       <c r="B4" s="256" t="inlineStr">
         <is>
-          <t>Дата</t>
+          <t>Спринт</t>
         </is>
       </c>
       <c r="C4" s="256" t="inlineStr">
         <is>
-          <t>Элемент бэклога</t>
+          <t>Настроение (1–5)</t>
         </is>
       </c>
       <c r="D4" s="256" t="inlineStr">
         <is>
-          <t>Действие</t>
-        </is>
-      </c>
-      <c r="E4" s="256" t="inlineStr">
-        <is>
-          <t>Оценка (SP)</t>
-        </is>
-      </c>
-      <c r="F4" s="256" t="inlineStr">
-        <is>
-          <t>Готовность</t>
-        </is>
-      </c>
-      <c r="G4" s="256" t="inlineStr">
-        <is>
-          <t>Ответственный</t>
-        </is>
-      </c>
-      <c r="H4" s="256" t="inlineStr">
-        <is>
           <t>Комментарий</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="30" customHeight="1">
+    <row r="5" ht="28" customHeight="1">
       <c r="A5" s="260" t="inlineStr">
         <is>
-          <t>GR-01</t>
-        </is>
-      </c>
-      <c r="B5" s="260" t="inlineStr">
-        <is>
-          <t>2026-08-28</t>
-        </is>
-      </c>
-      <c r="C5" s="260" t="inlineStr">
-        <is>
-          <t>История: оформление заказа</t>
-        </is>
+          <t>MD-01</t>
+        </is>
+      </c>
+      <c r="B5" s="260" t="n">
+        <v>1</v>
+      </c>
+      <c r="C5" s="260" t="n">
+        <v>4</v>
       </c>
       <c r="D5" s="260" t="inlineStr">
         <is>
-          <t>Декомпозиция</t>
-        </is>
-      </c>
-      <c r="E5" s="260" t="n">
-        <v>8</v>
-      </c>
-      <c r="F5" s="260" t="inlineStr">
-        <is>
-          <t>Готово к спринту</t>
-        </is>
-      </c>
-      <c r="G5" s="260" t="inlineStr">
-        <is>
-          <t>Иванов А.</t>
-        </is>
-      </c>
-      <c r="H5" s="260" t="inlineStr">
-        <is>
-          <t>Разбита на 3 подзадачи; критерии приёмки уточнены</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="30" customHeight="1">
+          <t>Хороший старт, понятные цели</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="28" customHeight="1">
       <c r="A6" s="260" t="inlineStr">
         <is>
-          <t>GR-02</t>
-        </is>
-      </c>
-      <c r="B6" s="260" t="inlineStr">
-        <is>
-          <t>2026-08-28</t>
-        </is>
-      </c>
-      <c r="C6" s="260" t="inlineStr">
-        <is>
-          <t>История: оплата картой</t>
-        </is>
+          <t>MD-02</t>
+        </is>
+      </c>
+      <c r="B6" s="260" t="n">
+        <v>2</v>
+      </c>
+      <c r="C6" s="260" t="n">
+        <v>3</v>
       </c>
       <c r="D6" s="260" t="inlineStr">
         <is>
-          <t>Оценка</t>
-        </is>
-      </c>
-      <c r="E6" s="260" t="n">
-        <v>5</v>
-      </c>
-      <c r="F6" s="260" t="inlineStr">
-        <is>
-          <t>Готово к спринту</t>
-        </is>
-      </c>
-      <c r="G6" s="260" t="inlineStr">
-        <is>
-          <t>Кузнецов Д.</t>
-        </is>
-      </c>
-      <c r="H6" s="260" t="inlineStr">
-        <is>
-          <t>Оценка по покеру, риск интеграции учтён</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="30" customHeight="1">
+          <t>Много переключений между задачами</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="28" customHeight="1">
       <c r="A7" s="260" t="inlineStr">
         <is>
-          <t>GR-03</t>
-        </is>
-      </c>
-      <c r="B7" s="260" t="inlineStr">
-        <is>
-          <t>2026-08-28</t>
-        </is>
-      </c>
-      <c r="C7" s="260" t="inlineStr">
-        <is>
-          <t>История: промокоды</t>
-        </is>
+          <t>MD-03</t>
+        </is>
+      </c>
+      <c r="B7" s="260" t="n">
+        <v>3</v>
+      </c>
+      <c r="C7" s="260" t="n">
+        <v>4</v>
       </c>
       <c r="D7" s="260" t="inlineStr">
         <is>
-          <t>Уточнение</t>
-        </is>
-      </c>
-      <c r="E7" s="260" t="n">
-        <v>3</v>
-      </c>
-      <c r="F7" s="260" t="inlineStr">
-        <is>
-          <t>Требует доработки</t>
-        </is>
-      </c>
-      <c r="G7" s="260" t="inlineStr">
-        <is>
-          <t>Петрова М.</t>
-        </is>
-      </c>
-      <c r="H7" s="260" t="inlineStr">
-        <is>
-          <t>Нужны правила комбинирования скидок от заказчика</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="30" customHeight="1">
-      <c r="A8" s="260" t="inlineStr">
-        <is>
-          <t>GR-04</t>
-        </is>
-      </c>
-      <c r="B8" s="260" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="C8" s="260" t="inlineStr">
-        <is>
-          <t>Фича: рекомендации товаров</t>
-        </is>
-      </c>
-      <c r="D8" s="260" t="inlineStr">
-        <is>
-          <t>Приоритизация</t>
-        </is>
-      </c>
-      <c r="E8" s="260" t="n">
-        <v>13</v>
-      </c>
-      <c r="F8" s="260" t="inlineStr">
-        <is>
-          <t>Требует доработки</t>
-        </is>
-      </c>
-      <c r="G8" s="260" t="inlineStr">
-        <is>
-          <t>Орлова Е.</t>
-        </is>
-      </c>
-      <c r="H8" s="260" t="inlineStr">
-        <is>
-          <t>Отложено: зависит от аналитики поведения</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="30" customHeight="1">
-      <c r="A9" s="260" t="inlineStr">
-        <is>
-          <t>GR-05</t>
-        </is>
-      </c>
-      <c r="B9" s="260" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="C9" s="260" t="inlineStr">
-        <is>
-          <t>История: история заказов</t>
-        </is>
-      </c>
-      <c r="D9" s="260" t="inlineStr">
-        <is>
-          <t>Оценка</t>
-        </is>
-      </c>
-      <c r="E9" s="260" t="n">
-        <v>5</v>
-      </c>
-      <c r="F9" s="260" t="inlineStr">
-        <is>
-          <t>Готово к спринту</t>
-        </is>
-      </c>
-      <c r="G9" s="260" t="inlineStr">
-        <is>
-          <t>Соколов Р.</t>
-        </is>
-      </c>
-      <c r="H9" s="260" t="inlineStr">
-        <is>
-          <t>Готова к взятию в спринт 4</t>
+          <t>Наладили процесс, меньше блокеров</t>
         </is>
       </c>
     </row>
@@ -47340,6 +47170,732 @@
 </file>
 
 <file path=xl/worksheets/sheet34.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="9" customWidth="1" min="1" max="1"/>
+    <col width="9" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="44" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="213" t="inlineStr">
+        <is>
+          <t>Kudos — благодарности</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="225" t="inlineStr">
+        <is>
+          <t>Публичное признание вклада коллег на ретроспективе.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="256" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B4" s="256" t="inlineStr">
+        <is>
+          <t>Спринт</t>
+        </is>
+      </c>
+      <c r="C4" s="256" t="inlineStr">
+        <is>
+          <t>От кого</t>
+        </is>
+      </c>
+      <c r="D4" s="256" t="inlineStr">
+        <is>
+          <t>Кому</t>
+        </is>
+      </c>
+      <c r="E4" s="256" t="inlineStr">
+        <is>
+          <t>За что</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="28" customHeight="1">
+      <c r="A5" s="260" t="inlineStr">
+        <is>
+          <t>KD-01</t>
+        </is>
+      </c>
+      <c r="B5" s="260" t="n">
+        <v>3</v>
+      </c>
+      <c r="C5" s="260" t="inlineStr">
+        <is>
+          <t>Команда</t>
+        </is>
+      </c>
+      <c r="D5" s="260" t="inlineStr">
+        <is>
+          <t>Кузнецов Д.</t>
+        </is>
+      </c>
+      <c r="E5" s="260" t="inlineStr">
+        <is>
+          <t>Быстро поднял платёжную интеграцию</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="28" customHeight="1">
+      <c r="A6" s="260" t="inlineStr">
+        <is>
+          <t>KD-02</t>
+        </is>
+      </c>
+      <c r="B6" s="260" t="n">
+        <v>3</v>
+      </c>
+      <c r="C6" s="260" t="inlineStr">
+        <is>
+          <t>Петрова М.</t>
+        </is>
+      </c>
+      <c r="D6" s="260" t="inlineStr">
+        <is>
+          <t>Соколов Р.</t>
+        </is>
+      </c>
+      <c r="E6" s="260" t="inlineStr">
+        <is>
+          <t>Помог с регрессом в выходной</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="28" customHeight="1">
+      <c r="A7" s="260" t="inlineStr">
+        <is>
+          <t>KD-03</t>
+        </is>
+      </c>
+      <c r="B7" s="260" t="n">
+        <v>2</v>
+      </c>
+      <c r="C7" s="260" t="inlineStr">
+        <is>
+          <t>PO</t>
+        </is>
+      </c>
+      <c r="D7" s="260" t="inlineStr">
+        <is>
+          <t>Команда</t>
+        </is>
+      </c>
+      <c r="E7" s="260" t="inlineStr">
+        <is>
+          <t>Отличное демо корзины</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet35.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="9" customWidth="1" min="1" max="1"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="28" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="213" t="inlineStr">
+        <is>
+          <t>Эксперименты — проверяемые улучшения</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="225" t="inlineStr">
+        <is>
+          <t>Гипотеза → действие → метрика → результат.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="256" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B4" s="256" t="inlineStr">
+        <is>
+          <t>Спринт</t>
+        </is>
+      </c>
+      <c r="C4" s="256" t="inlineStr">
+        <is>
+          <t>Гипотеза</t>
+        </is>
+      </c>
+      <c r="D4" s="256" t="inlineStr">
+        <is>
+          <t>Действие</t>
+        </is>
+      </c>
+      <c r="E4" s="256" t="inlineStr">
+        <is>
+          <t>Метрика</t>
+        </is>
+      </c>
+      <c r="F4" s="256" t="inlineStr">
+        <is>
+          <t>Результат</t>
+        </is>
+      </c>
+      <c r="G4" s="256" t="inlineStr">
+        <is>
+          <t>Статус</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="28" customHeight="1">
+      <c r="A5" s="260" t="inlineStr">
+        <is>
+          <t>EX-01</t>
+        </is>
+      </c>
+      <c r="B5" s="260" t="n">
+        <v>2</v>
+      </c>
+      <c r="C5" s="260" t="inlineStr">
+        <is>
+          <t>Парное ревью ускорит закрытие сложных задач</t>
+        </is>
+      </c>
+      <c r="D5" s="260" t="inlineStr">
+        <is>
+          <t>Ввести парное ревью для сложных PR</t>
+        </is>
+      </c>
+      <c r="E5" s="260" t="inlineStr">
+        <is>
+          <t>Cycle time сложных задач</t>
+        </is>
+      </c>
+      <c r="F5" s="260" t="inlineStr">
+        <is>
+          <t>Cycle time −15%</t>
+        </is>
+      </c>
+      <c r="G5" s="260" t="inlineStr">
+        <is>
+          <t>Успешно</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="28" customHeight="1">
+      <c r="A6" s="260" t="inlineStr">
+        <is>
+          <t>EX-02</t>
+        </is>
+      </c>
+      <c r="B6" s="260" t="n">
+        <v>3</v>
+      </c>
+      <c r="C6" s="260" t="inlineStr">
+        <is>
+          <t>WIP-лимит снизит переключения и ускорит поток</t>
+        </is>
+      </c>
+      <c r="D6" s="260" t="inlineStr">
+        <is>
+          <t>Лимит 2 задачи «В работе» на человека</t>
+        </is>
+      </c>
+      <c r="E6" s="260" t="inlineStr">
+        <is>
+          <t>Число параллельных задач</t>
+        </is>
+      </c>
+      <c r="F6" s="260" t="inlineStr">
+        <is>
+          <t>В процессе замера</t>
+        </is>
+      </c>
+      <c r="G6" s="260" t="inlineStr">
+        <is>
+          <t>Идёт</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet36.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="9" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="213" t="inlineStr">
+        <is>
+          <t>Team Radar — самооценка команды</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="225" t="inlineStr">
+        <is>
+          <t>Оценка по осям 1–5: текущий и прошлый спринт.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="256" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B4" s="256" t="inlineStr">
+        <is>
+          <t>Ось</t>
+        </is>
+      </c>
+      <c r="C4" s="256" t="inlineStr">
+        <is>
+          <t>Сейчас (1–5)</t>
+        </is>
+      </c>
+      <c r="D4" s="256" t="inlineStr">
+        <is>
+          <t>Прошлый (1–5)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="28" customHeight="1">
+      <c r="A5" s="260" t="inlineStr">
+        <is>
+          <t>RD-01</t>
+        </is>
+      </c>
+      <c r="B5" s="260" t="inlineStr">
+        <is>
+          <t>Коммуникация</t>
+        </is>
+      </c>
+      <c r="C5" s="260" t="n">
+        <v>4</v>
+      </c>
+      <c r="D5" s="260" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6" ht="28" customHeight="1">
+      <c r="A6" s="260" t="inlineStr">
+        <is>
+          <t>RD-02</t>
+        </is>
+      </c>
+      <c r="B6" s="260" t="inlineStr">
+        <is>
+          <t>Качество</t>
+        </is>
+      </c>
+      <c r="C6" s="260" t="n">
+        <v>3</v>
+      </c>
+      <c r="D6" s="260" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="7" ht="28" customHeight="1">
+      <c r="A7" s="260" t="inlineStr">
+        <is>
+          <t>RD-03</t>
+        </is>
+      </c>
+      <c r="B7" s="260" t="inlineStr">
+        <is>
+          <t>Процесс</t>
+        </is>
+      </c>
+      <c r="C7" s="260" t="n">
+        <v>4</v>
+      </c>
+      <c r="D7" s="260" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="8" ht="28" customHeight="1">
+      <c r="A8" s="260" t="inlineStr">
+        <is>
+          <t>RD-04</t>
+        </is>
+      </c>
+      <c r="B8" s="260" t="inlineStr">
+        <is>
+          <t>Инструменты</t>
+        </is>
+      </c>
+      <c r="C8" s="260" t="n">
+        <v>4</v>
+      </c>
+      <c r="D8" s="260" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9" ht="28" customHeight="1">
+      <c r="A9" s="260" t="inlineStr">
+        <is>
+          <t>RD-05</t>
+        </is>
+      </c>
+      <c r="B9" s="260" t="inlineStr">
+        <is>
+          <t>Нагрузка</t>
+        </is>
+      </c>
+      <c r="C9" s="260" t="n">
+        <v>3</v>
+      </c>
+      <c r="D9" s="260" t="n">
+        <v>2</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet37.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="9" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="32" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="11" customWidth="1" min="6" max="6"/>
+    <col width="20" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
+    <col width="40" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="213" t="inlineStr">
+        <is>
+          <t>Груминг бэклога (Backlog Refinement)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="225" t="inlineStr">
+        <is>
+          <t>Подготовка элементов бэклога к спринту; задачи берутся из «Бэклога» (колонка «Задача»).</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="256" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B4" s="256" t="inlineStr">
+        <is>
+          <t>Задача (Бэклог)</t>
+        </is>
+      </c>
+      <c r="C4" s="256" t="inlineStr">
+        <is>
+          <t>Дата</t>
+        </is>
+      </c>
+      <c r="D4" s="256" t="inlineStr">
+        <is>
+          <t>Элемент бэклога</t>
+        </is>
+      </c>
+      <c r="E4" s="256" t="inlineStr">
+        <is>
+          <t>Действие</t>
+        </is>
+      </c>
+      <c r="F4" s="256" t="inlineStr">
+        <is>
+          <t>Оценка (SP)</t>
+        </is>
+      </c>
+      <c r="G4" s="256" t="inlineStr">
+        <is>
+          <t>Готовность</t>
+        </is>
+      </c>
+      <c r="H4" s="256" t="inlineStr">
+        <is>
+          <t>Ответственный</t>
+        </is>
+      </c>
+      <c r="I4" s="256" t="inlineStr">
+        <is>
+          <t>Комментарий</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="30" customHeight="1">
+      <c r="A5" s="260" t="inlineStr">
+        <is>
+          <t>GR-01</t>
+        </is>
+      </c>
+      <c r="B5" s="260" t="inlineStr">
+        <is>
+          <t>T-01</t>
+        </is>
+      </c>
+      <c r="C5" s="260" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="D5" s="260" t="inlineStr">
+        <is>
+          <t>История: оформление заказа</t>
+        </is>
+      </c>
+      <c r="E5" s="260" t="inlineStr">
+        <is>
+          <t>Декомпозиция</t>
+        </is>
+      </c>
+      <c r="F5" s="260" t="n">
+        <v>8</v>
+      </c>
+      <c r="G5" s="260" t="inlineStr">
+        <is>
+          <t>Готово к спринту</t>
+        </is>
+      </c>
+      <c r="H5" s="260" t="inlineStr">
+        <is>
+          <t>Иванов А.</t>
+        </is>
+      </c>
+      <c r="I5" s="260" t="inlineStr">
+        <is>
+          <t>Разбита на 3 подзадачи; критерии приёмки уточнены</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="30" customHeight="1">
+      <c r="A6" s="260" t="inlineStr">
+        <is>
+          <t>GR-02</t>
+        </is>
+      </c>
+      <c r="B6" s="260" t="inlineStr">
+        <is>
+          <t>T-03</t>
+        </is>
+      </c>
+      <c r="C6" s="260" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="D6" s="260" t="inlineStr">
+        <is>
+          <t>История: оплата картой</t>
+        </is>
+      </c>
+      <c r="E6" s="260" t="inlineStr">
+        <is>
+          <t>Оценка</t>
+        </is>
+      </c>
+      <c r="F6" s="260" t="n">
+        <v>5</v>
+      </c>
+      <c r="G6" s="260" t="inlineStr">
+        <is>
+          <t>Готово к спринту</t>
+        </is>
+      </c>
+      <c r="H6" s="260" t="inlineStr">
+        <is>
+          <t>Кузнецов Д.</t>
+        </is>
+      </c>
+      <c r="I6" s="260" t="inlineStr">
+        <is>
+          <t>Оценка по покеру, риск интеграции учтён</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="30" customHeight="1">
+      <c r="A7" s="260" t="inlineStr">
+        <is>
+          <t>GR-03</t>
+        </is>
+      </c>
+      <c r="B7" s="260" t="inlineStr"/>
+      <c r="C7" s="260" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="D7" s="260" t="inlineStr">
+        <is>
+          <t>История: промокоды</t>
+        </is>
+      </c>
+      <c r="E7" s="260" t="inlineStr">
+        <is>
+          <t>Уточнение</t>
+        </is>
+      </c>
+      <c r="F7" s="260" t="n">
+        <v>3</v>
+      </c>
+      <c r="G7" s="260" t="inlineStr">
+        <is>
+          <t>Требует доработки</t>
+        </is>
+      </c>
+      <c r="H7" s="260" t="inlineStr">
+        <is>
+          <t>Петрова М.</t>
+        </is>
+      </c>
+      <c r="I7" s="260" t="inlineStr">
+        <is>
+          <t>Нужны правила комбинирования скидок от заказчика</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="30" customHeight="1">
+      <c r="A8" s="260" t="inlineStr">
+        <is>
+          <t>GR-04</t>
+        </is>
+      </c>
+      <c r="B8" s="260" t="inlineStr"/>
+      <c r="C8" s="260" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="D8" s="260" t="inlineStr">
+        <is>
+          <t>Фича: рекомендации товаров</t>
+        </is>
+      </c>
+      <c r="E8" s="260" t="inlineStr">
+        <is>
+          <t>Приоритизация</t>
+        </is>
+      </c>
+      <c r="F8" s="260" t="n">
+        <v>13</v>
+      </c>
+      <c r="G8" s="260" t="inlineStr">
+        <is>
+          <t>Требует доработки</t>
+        </is>
+      </c>
+      <c r="H8" s="260" t="inlineStr">
+        <is>
+          <t>Орлова Е.</t>
+        </is>
+      </c>
+      <c r="I8" s="260" t="inlineStr">
+        <is>
+          <t>Отложено: зависит от аналитики поведения</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="30" customHeight="1">
+      <c r="A9" s="260" t="inlineStr">
+        <is>
+          <t>GR-05</t>
+        </is>
+      </c>
+      <c r="B9" s="260" t="inlineStr"/>
+      <c r="C9" s="260" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="D9" s="260" t="inlineStr">
+        <is>
+          <t>История: история заказов</t>
+        </is>
+      </c>
+      <c r="E9" s="260" t="inlineStr">
+        <is>
+          <t>Оценка</t>
+        </is>
+      </c>
+      <c r="F9" s="260" t="n">
+        <v>5</v>
+      </c>
+      <c r="G9" s="260" t="inlineStr">
+        <is>
+          <t>Готово к спринту</t>
+        </is>
+      </c>
+      <c r="H9" s="260" t="inlineStr">
+        <is>
+          <t>Соколов Р.</t>
+        </is>
+      </c>
+      <c r="I9" s="260" t="inlineStr">
+        <is>
+          <t>Готова к взятию в спринт 4</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet38.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -47539,7 +48095,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet35.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet39.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -47768,698 +48324,6 @@
       <c r="G9" s="260" t="inlineStr">
         <is>
           <t>Нестабильный стенд QA</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet36.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:H9"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="9" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="8" customWidth="1" min="6" max="6"/>
-    <col width="15" customWidth="1" min="7" max="7"/>
-    <col width="34" customWidth="1" min="8" max="8"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="213" t="inlineStr">
-        <is>
-          <t>График отпусков и отсутствий</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="225" t="inlineStr">
-        <is>
-          <t>Отпуска, больничные, отгулы и командировки — для учёта доступности команды.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="256" t="inlineStr">
-        <is>
-          <t>ID</t>
-        </is>
-      </c>
-      <c r="B4" s="256" t="inlineStr">
-        <is>
-          <t>Участник</t>
-        </is>
-      </c>
-      <c r="C4" s="256" t="inlineStr">
-        <is>
-          <t>Тип</t>
-        </is>
-      </c>
-      <c r="D4" s="256" t="inlineStr">
-        <is>
-          <t>С</t>
-        </is>
-      </c>
-      <c r="E4" s="256" t="inlineStr">
-        <is>
-          <t>По</t>
-        </is>
-      </c>
-      <c r="F4" s="256" t="inlineStr">
-        <is>
-          <t>Дней</t>
-        </is>
-      </c>
-      <c r="G4" s="256" t="inlineStr">
-        <is>
-          <t>Статус</t>
-        </is>
-      </c>
-      <c r="H4" s="256" t="inlineStr">
-        <is>
-          <t>Комментарий</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="30" customHeight="1">
-      <c r="A5" s="260" t="inlineStr">
-        <is>
-          <t>VC-01</t>
-        </is>
-      </c>
-      <c r="B5" s="260" t="inlineStr">
-        <is>
-          <t>Иванов А.</t>
-        </is>
-      </c>
-      <c r="C5" s="260" t="inlineStr">
-        <is>
-          <t>Отпуск</t>
-        </is>
-      </c>
-      <c r="D5" s="260" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="E5" s="260" t="inlineStr">
-        <is>
-          <t>2026-10-03</t>
-        </is>
-      </c>
-      <c r="F5" s="260" t="n">
-        <v>10</v>
-      </c>
-      <c r="G5" s="260" t="inlineStr">
-        <is>
-          <t>Утверждён</t>
-        </is>
-      </c>
-      <c r="H5" s="260" t="inlineStr">
-        <is>
-          <t>Плановый отпуск</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="30" customHeight="1">
-      <c r="A6" s="260" t="inlineStr">
-        <is>
-          <t>VC-02</t>
-        </is>
-      </c>
-      <c r="B6" s="260" t="inlineStr">
-        <is>
-          <t>Петрова М.</t>
-        </is>
-      </c>
-      <c r="C6" s="260" t="inlineStr">
-        <is>
-          <t>Отгул</t>
-        </is>
-      </c>
-      <c r="D6" s="260" t="inlineStr">
-        <is>
-          <t>2026-09-18</t>
-        </is>
-      </c>
-      <c r="E6" s="260" t="inlineStr">
-        <is>
-          <t>2026-09-18</t>
-        </is>
-      </c>
-      <c r="F6" s="260" t="n">
-        <v>1</v>
-      </c>
-      <c r="G6" s="260" t="inlineStr">
-        <is>
-          <t>Утверждён</t>
-        </is>
-      </c>
-      <c r="H6" s="260" t="inlineStr"/>
-    </row>
-    <row r="7" ht="30" customHeight="1">
-      <c r="A7" s="260" t="inlineStr">
-        <is>
-          <t>VC-03</t>
-        </is>
-      </c>
-      <c r="B7" s="260" t="inlineStr">
-        <is>
-          <t>Кузнецов Д.</t>
-        </is>
-      </c>
-      <c r="C7" s="260" t="inlineStr">
-        <is>
-          <t>Командировка</t>
-        </is>
-      </c>
-      <c r="D7" s="260" t="inlineStr">
-        <is>
-          <t>2026-09-29</t>
-        </is>
-      </c>
-      <c r="E7" s="260" t="inlineStr">
-        <is>
-          <t>2026-10-01</t>
-        </is>
-      </c>
-      <c r="F7" s="260" t="n">
-        <v>3</v>
-      </c>
-      <c r="G7" s="260" t="inlineStr">
-        <is>
-          <t>Запланирован</t>
-        </is>
-      </c>
-      <c r="H7" s="260" t="inlineStr">
-        <is>
-          <t>Встреча с платёжным провайдером</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="30" customHeight="1">
-      <c r="A8" s="260" t="inlineStr">
-        <is>
-          <t>VC-04</t>
-        </is>
-      </c>
-      <c r="B8" s="260" t="inlineStr">
-        <is>
-          <t>Орлова Е.</t>
-        </is>
-      </c>
-      <c r="C8" s="260" t="inlineStr">
-        <is>
-          <t>Больничный</t>
-        </is>
-      </c>
-      <c r="D8" s="260" t="inlineStr">
-        <is>
-          <t>2026-09-08</t>
-        </is>
-      </c>
-      <c r="E8" s="260" t="inlineStr">
-        <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="F8" s="260" t="n">
-        <v>3</v>
-      </c>
-      <c r="G8" s="260" t="inlineStr">
-        <is>
-          <t>Завершён</t>
-        </is>
-      </c>
-      <c r="H8" s="260" t="inlineStr"/>
-    </row>
-    <row r="9" ht="30" customHeight="1">
-      <c r="A9" s="260" t="inlineStr">
-        <is>
-          <t>VC-05</t>
-        </is>
-      </c>
-      <c r="B9" s="260" t="inlineStr">
-        <is>
-          <t>Соколов Р.</t>
-        </is>
-      </c>
-      <c r="C9" s="260" t="inlineStr">
-        <is>
-          <t>Отпуск</t>
-        </is>
-      </c>
-      <c r="D9" s="260" t="inlineStr">
-        <is>
-          <t>2026-10-13</t>
-        </is>
-      </c>
-      <c r="E9" s="260" t="inlineStr">
-        <is>
-          <t>2026-10-24</t>
-        </is>
-      </c>
-      <c r="F9" s="260" t="n">
-        <v>10</v>
-      </c>
-      <c r="G9" s="260" t="inlineStr">
-        <is>
-          <t>Запланирован</t>
-        </is>
-      </c>
-      <c r="H9" s="260" t="inlineStr"/>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet37.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:E9"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="9" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
-    <col width="15" customWidth="1" min="4" max="4"/>
-    <col width="34" customWidth="1" min="5" max="5"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="213" t="inlineStr">
-        <is>
-          <t>Дни рождения команды</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="225" t="inlineStr">
-        <is>
-          <t>Даты рождения участников; в приложении показываются ближайшие даты с обратным отсчётом.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="256" t="inlineStr">
-        <is>
-          <t>ID</t>
-        </is>
-      </c>
-      <c r="B4" s="256" t="inlineStr">
-        <is>
-          <t>Участник</t>
-        </is>
-      </c>
-      <c r="C4" s="256" t="inlineStr">
-        <is>
-          <t>Дата рождения</t>
-        </is>
-      </c>
-      <c r="D4" s="256" t="inlineStr">
-        <is>
-          <t>Роль</t>
-        </is>
-      </c>
-      <c r="E4" s="256" t="inlineStr">
-        <is>
-          <t>Комментарий</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="30" customHeight="1">
-      <c r="A5" s="260" t="inlineStr">
-        <is>
-          <t>BD-01</t>
-        </is>
-      </c>
-      <c r="B5" s="260" t="inlineStr">
-        <is>
-          <t>Иванов А.</t>
-        </is>
-      </c>
-      <c r="C5" s="260" t="inlineStr">
-        <is>
-          <t>1990-09-20</t>
-        </is>
-      </c>
-      <c r="D5" s="260" t="inlineStr">
-        <is>
-          <t>Backend</t>
-        </is>
-      </c>
-      <c r="E5" s="260" t="inlineStr"/>
-    </row>
-    <row r="6" ht="30" customHeight="1">
-      <c r="A6" s="260" t="inlineStr">
-        <is>
-          <t>BD-02</t>
-        </is>
-      </c>
-      <c r="B6" s="260" t="inlineStr">
-        <is>
-          <t>Петрова М.</t>
-        </is>
-      </c>
-      <c r="C6" s="260" t="inlineStr">
-        <is>
-          <t>1993-10-05</t>
-        </is>
-      </c>
-      <c r="D6" s="260" t="inlineStr">
-        <is>
-          <t>Frontend</t>
-        </is>
-      </c>
-      <c r="E6" s="260" t="inlineStr"/>
-    </row>
-    <row r="7" ht="30" customHeight="1">
-      <c r="A7" s="260" t="inlineStr">
-        <is>
-          <t>BD-03</t>
-        </is>
-      </c>
-      <c r="B7" s="260" t="inlineStr">
-        <is>
-          <t>Кузнецов Д.</t>
-        </is>
-      </c>
-      <c r="C7" s="260" t="inlineStr">
-        <is>
-          <t>1988-11-12</t>
-        </is>
-      </c>
-      <c r="D7" s="260" t="inlineStr">
-        <is>
-          <t>Backend</t>
-        </is>
-      </c>
-      <c r="E7" s="260" t="inlineStr"/>
-    </row>
-    <row r="8" ht="30" customHeight="1">
-      <c r="A8" s="260" t="inlineStr">
-        <is>
-          <t>BD-04</t>
-        </is>
-      </c>
-      <c r="B8" s="260" t="inlineStr">
-        <is>
-          <t>Орлова Е.</t>
-        </is>
-      </c>
-      <c r="C8" s="260" t="inlineStr">
-        <is>
-          <t>1995-09-28</t>
-        </is>
-      </c>
-      <c r="D8" s="260" t="inlineStr">
-        <is>
-          <t>Analyst</t>
-        </is>
-      </c>
-      <c r="E8" s="260" t="inlineStr"/>
-    </row>
-    <row r="9" ht="30" customHeight="1">
-      <c r="A9" s="260" t="inlineStr">
-        <is>
-          <t>BD-05</t>
-        </is>
-      </c>
-      <c r="B9" s="260" t="inlineStr">
-        <is>
-          <t>Соколов Р.</t>
-        </is>
-      </c>
-      <c r="C9" s="260" t="inlineStr">
-        <is>
-          <t>1991-12-03</t>
-        </is>
-      </c>
-      <c r="D9" s="260" t="inlineStr">
-        <is>
-          <t>QA</t>
-        </is>
-      </c>
-      <c r="E9" s="260" t="inlineStr"/>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet38.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:D7"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="9" customWidth="1" min="1" max="1"/>
-    <col width="9" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="44" customWidth="1" min="4" max="4"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="213" t="inlineStr">
-        <is>
-          <t>Настроение команды по спринтам</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="225" t="inlineStr">
-        <is>
-          <t>Оценка климата спринта (1–5) — в приложении показывается трендом.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="256" t="inlineStr">
-        <is>
-          <t>ID</t>
-        </is>
-      </c>
-      <c r="B4" s="256" t="inlineStr">
-        <is>
-          <t>Спринт</t>
-        </is>
-      </c>
-      <c r="C4" s="256" t="inlineStr">
-        <is>
-          <t>Настроение (1–5)</t>
-        </is>
-      </c>
-      <c r="D4" s="256" t="inlineStr">
-        <is>
-          <t>Комментарий</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="28" customHeight="1">
-      <c r="A5" s="260" t="inlineStr">
-        <is>
-          <t>MD-01</t>
-        </is>
-      </c>
-      <c r="B5" s="260" t="n">
-        <v>1</v>
-      </c>
-      <c r="C5" s="260" t="n">
-        <v>4</v>
-      </c>
-      <c r="D5" s="260" t="inlineStr">
-        <is>
-          <t>Хороший старт, понятные цели</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="28" customHeight="1">
-      <c r="A6" s="260" t="inlineStr">
-        <is>
-          <t>MD-02</t>
-        </is>
-      </c>
-      <c r="B6" s="260" t="n">
-        <v>2</v>
-      </c>
-      <c r="C6" s="260" t="n">
-        <v>3</v>
-      </c>
-      <c r="D6" s="260" t="inlineStr">
-        <is>
-          <t>Много переключений между задачами</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="28" customHeight="1">
-      <c r="A7" s="260" t="inlineStr">
-        <is>
-          <t>MD-03</t>
-        </is>
-      </c>
-      <c r="B7" s="260" t="n">
-        <v>3</v>
-      </c>
-      <c r="C7" s="260" t="n">
-        <v>4</v>
-      </c>
-      <c r="D7" s="260" t="inlineStr">
-        <is>
-          <t>Наладили процесс, меньше блокеров</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet39.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:E7"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="9" customWidth="1" min="1" max="1"/>
-    <col width="9" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="44" customWidth="1" min="5" max="5"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="213" t="inlineStr">
-        <is>
-          <t>Kudos — благодарности</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="225" t="inlineStr">
-        <is>
-          <t>Публичное признание вклада коллег на ретроспективе.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="256" t="inlineStr">
-        <is>
-          <t>ID</t>
-        </is>
-      </c>
-      <c r="B4" s="256" t="inlineStr">
-        <is>
-          <t>Спринт</t>
-        </is>
-      </c>
-      <c r="C4" s="256" t="inlineStr">
-        <is>
-          <t>От кого</t>
-        </is>
-      </c>
-      <c r="D4" s="256" t="inlineStr">
-        <is>
-          <t>Кому</t>
-        </is>
-      </c>
-      <c r="E4" s="256" t="inlineStr">
-        <is>
-          <t>За что</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="28" customHeight="1">
-      <c r="A5" s="260" t="inlineStr">
-        <is>
-          <t>KD-01</t>
-        </is>
-      </c>
-      <c r="B5" s="260" t="n">
-        <v>3</v>
-      </c>
-      <c r="C5" s="260" t="inlineStr">
-        <is>
-          <t>Команда</t>
-        </is>
-      </c>
-      <c r="D5" s="260" t="inlineStr">
-        <is>
-          <t>Кузнецов Д.</t>
-        </is>
-      </c>
-      <c r="E5" s="260" t="inlineStr">
-        <is>
-          <t>Быстро поднял платёжную интеграцию</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="28" customHeight="1">
-      <c r="A6" s="260" t="inlineStr">
-        <is>
-          <t>KD-02</t>
-        </is>
-      </c>
-      <c r="B6" s="260" t="n">
-        <v>3</v>
-      </c>
-      <c r="C6" s="260" t="inlineStr">
-        <is>
-          <t>Петрова М.</t>
-        </is>
-      </c>
-      <c r="D6" s="260" t="inlineStr">
-        <is>
-          <t>Соколов Р.</t>
-        </is>
-      </c>
-      <c r="E6" s="260" t="inlineStr">
-        <is>
-          <t>Помог с регрессом в выходной</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="28" customHeight="1">
-      <c r="A7" s="260" t="inlineStr">
-        <is>
-          <t>KD-03</t>
-        </is>
-      </c>
-      <c r="B7" s="260" t="n">
-        <v>2</v>
-      </c>
-      <c r="C7" s="260" t="inlineStr">
-        <is>
-          <t>PO</t>
-        </is>
-      </c>
-      <c r="D7" s="260" t="inlineStr">
-        <is>
-          <t>Команда</t>
-        </is>
-      </c>
-      <c r="E7" s="260" t="inlineStr">
-        <is>
-          <t>Отличное демо корзины</t>
         </is>
       </c>
     </row>
@@ -50354,29 +50218,30 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:H9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
-    <col width="8" customWidth="1" min="2" max="2"/>
-    <col width="30" customWidth="1" min="3" max="3"/>
-    <col width="28" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="22" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="8" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="34" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="213" t="inlineStr">
         <is>
-          <t>Эксперименты — проверяемые улучшения</t>
+          <t>График отпусков и отсутствий</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="225" t="inlineStr">
         <is>
-          <t>Гипотеза → действие → метрика → результат.</t>
+          <t>Отпуска, больничные, отгулы и командировки — для учёта доступности команды.</t>
         </is>
       </c>
     </row>
@@ -50388,27 +50253,27 @@
       </c>
       <c r="B4" s="256" t="inlineStr">
         <is>
-          <t>Спринт</t>
+          <t>Участник</t>
         </is>
       </c>
       <c r="C4" s="256" t="inlineStr">
         <is>
-          <t>Гипотеза</t>
+          <t>Тип</t>
         </is>
       </c>
       <c r="D4" s="256" t="inlineStr">
         <is>
-          <t>Действие</t>
+          <t>С</t>
         </is>
       </c>
       <c r="E4" s="256" t="inlineStr">
         <is>
-          <t>Метрика</t>
+          <t>По</t>
         </is>
       </c>
       <c r="F4" s="256" t="inlineStr">
         <is>
-          <t>Результат</t>
+          <t>Дней</t>
         </is>
       </c>
       <c r="G4" s="256" t="inlineStr">
@@ -50416,76 +50281,199 @@
           <t>Статус</t>
         </is>
       </c>
-    </row>
-    <row r="5" ht="28" customHeight="1">
+      <c r="H4" s="256" t="inlineStr">
+        <is>
+          <t>Комментарий</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="30" customHeight="1">
       <c r="A5" s="260" t="inlineStr">
         <is>
-          <t>EX-01</t>
-        </is>
-      </c>
-      <c r="B5" s="260" t="n">
-        <v>2</v>
+          <t>VC-01</t>
+        </is>
+      </c>
+      <c r="B5" s="260" t="inlineStr">
+        <is>
+          <t>Иванов А.</t>
+        </is>
       </c>
       <c r="C5" s="260" t="inlineStr">
         <is>
-          <t>Парное ревью ускорит закрытие сложных задач</t>
+          <t>Отпуск</t>
         </is>
       </c>
       <c r="D5" s="260" t="inlineStr">
         <is>
-          <t>Ввести парное ревью для сложных PR</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="E5" s="260" t="inlineStr">
         <is>
-          <t>Cycle time сложных задач</t>
-        </is>
-      </c>
-      <c r="F5" s="260" t="inlineStr">
-        <is>
-          <t>Cycle time −15%</t>
-        </is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="F5" s="260" t="n">
+        <v>10</v>
       </c>
       <c r="G5" s="260" t="inlineStr">
         <is>
-          <t>Успешно</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="28" customHeight="1">
+          <t>Утверждён</t>
+        </is>
+      </c>
+      <c r="H5" s="260" t="inlineStr">
+        <is>
+          <t>Плановый отпуск</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="30" customHeight="1">
       <c r="A6" s="260" t="inlineStr">
         <is>
-          <t>EX-02</t>
-        </is>
-      </c>
-      <c r="B6" s="260" t="n">
+          <t>VC-02</t>
+        </is>
+      </c>
+      <c r="B6" s="260" t="inlineStr">
+        <is>
+          <t>Петрова М.</t>
+        </is>
+      </c>
+      <c r="C6" s="260" t="inlineStr">
+        <is>
+          <t>Отгул</t>
+        </is>
+      </c>
+      <c r="D6" s="260" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="E6" s="260" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="F6" s="260" t="n">
+        <v>1</v>
+      </c>
+      <c r="G6" s="260" t="inlineStr">
+        <is>
+          <t>Утверждён</t>
+        </is>
+      </c>
+      <c r="H6" s="260" t="inlineStr"/>
+    </row>
+    <row r="7" ht="30" customHeight="1">
+      <c r="A7" s="260" t="inlineStr">
+        <is>
+          <t>VC-03</t>
+        </is>
+      </c>
+      <c r="B7" s="260" t="inlineStr">
+        <is>
+          <t>Кузнецов Д.</t>
+        </is>
+      </c>
+      <c r="C7" s="260" t="inlineStr">
+        <is>
+          <t>Командировка</t>
+        </is>
+      </c>
+      <c r="D7" s="260" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="E7" s="260" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="F7" s="260" t="n">
         <v>3</v>
       </c>
-      <c r="C6" s="260" t="inlineStr">
-        <is>
-          <t>WIP-лимит снизит переключения и ускорит поток</t>
-        </is>
-      </c>
-      <c r="D6" s="260" t="inlineStr">
-        <is>
-          <t>Лимит 2 задачи «В работе» на человека</t>
-        </is>
-      </c>
-      <c r="E6" s="260" t="inlineStr">
-        <is>
-          <t>Число параллельных задач</t>
-        </is>
-      </c>
-      <c r="F6" s="260" t="inlineStr">
-        <is>
-          <t>В процессе замера</t>
-        </is>
-      </c>
-      <c r="G6" s="260" t="inlineStr">
-        <is>
-          <t>Идёт</t>
-        </is>
-      </c>
+      <c r="G7" s="260" t="inlineStr">
+        <is>
+          <t>Запланирован</t>
+        </is>
+      </c>
+      <c r="H7" s="260" t="inlineStr">
+        <is>
+          <t>Встреча с платёжным провайдером</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="30" customHeight="1">
+      <c r="A8" s="260" t="inlineStr">
+        <is>
+          <t>VC-04</t>
+        </is>
+      </c>
+      <c r="B8" s="260" t="inlineStr">
+        <is>
+          <t>Орлова Е.</t>
+        </is>
+      </c>
+      <c r="C8" s="260" t="inlineStr">
+        <is>
+          <t>Больничный</t>
+        </is>
+      </c>
+      <c r="D8" s="260" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="E8" s="260" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="F8" s="260" t="n">
+        <v>3</v>
+      </c>
+      <c r="G8" s="260" t="inlineStr">
+        <is>
+          <t>Завершён</t>
+        </is>
+      </c>
+      <c r="H8" s="260" t="inlineStr"/>
+    </row>
+    <row r="9" ht="30" customHeight="1">
+      <c r="A9" s="260" t="inlineStr">
+        <is>
+          <t>VC-05</t>
+        </is>
+      </c>
+      <c r="B9" s="260" t="inlineStr">
+        <is>
+          <t>Соколов Р.</t>
+        </is>
+      </c>
+      <c r="C9" s="260" t="inlineStr">
+        <is>
+          <t>Отпуск</t>
+        </is>
+      </c>
+      <c r="D9" s="260" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="E9" s="260" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="F9" s="260" t="n">
+        <v>10</v>
+      </c>
+      <c r="G9" s="260" t="inlineStr">
+        <is>
+          <t>Запланирован</t>
+        </is>
+      </c>
+      <c r="H9" s="260" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -50498,26 +50486,27 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D9"/>
+  <dimension ref="A1:E9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="34" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="213" t="inlineStr">
         <is>
-          <t>Team Radar — самооценка команды</t>
+          <t>Дни рождения команды</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="225" t="inlineStr">
         <is>
-          <t>Оценка по осям 1–5: текущий и прошлый спринт.</t>
+          <t>Даты рождения участников; в приложении показываются ближайшие даты с обратным отсчётом.</t>
         </is>
       </c>
     </row>
@@ -50529,109 +50518,139 @@
       </c>
       <c r="B4" s="256" t="inlineStr">
         <is>
-          <t>Ось</t>
+          <t>Участник</t>
         </is>
       </c>
       <c r="C4" s="256" t="inlineStr">
         <is>
-          <t>Сейчас (1–5)</t>
+          <t>Дата рождения</t>
         </is>
       </c>
       <c r="D4" s="256" t="inlineStr">
         <is>
-          <t>Прошлый (1–5)</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="28" customHeight="1">
+          <t>Роль</t>
+        </is>
+      </c>
+      <c r="E4" s="256" t="inlineStr">
+        <is>
+          <t>Комментарий</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="30" customHeight="1">
       <c r="A5" s="260" t="inlineStr">
         <is>
-          <t>RD-01</t>
+          <t>BD-01</t>
         </is>
       </c>
       <c r="B5" s="260" t="inlineStr">
         <is>
-          <t>Коммуникация</t>
-        </is>
-      </c>
-      <c r="C5" s="260" t="n">
-        <v>4</v>
-      </c>
-      <c r="D5" s="260" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="6" ht="28" customHeight="1">
+          <t>Иванов А.</t>
+        </is>
+      </c>
+      <c r="C5" s="260" t="inlineStr">
+        <is>
+          <t>1990-09-20</t>
+        </is>
+      </c>
+      <c r="D5" s="260" t="inlineStr">
+        <is>
+          <t>Backend</t>
+        </is>
+      </c>
+      <c r="E5" s="260" t="inlineStr"/>
+    </row>
+    <row r="6" ht="30" customHeight="1">
       <c r="A6" s="260" t="inlineStr">
         <is>
-          <t>RD-02</t>
+          <t>BD-02</t>
         </is>
       </c>
       <c r="B6" s="260" t="inlineStr">
         <is>
-          <t>Качество</t>
-        </is>
-      </c>
-      <c r="C6" s="260" t="n">
-        <v>3</v>
-      </c>
-      <c r="D6" s="260" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="7" ht="28" customHeight="1">
+          <t>Петрова М.</t>
+        </is>
+      </c>
+      <c r="C6" s="260" t="inlineStr">
+        <is>
+          <t>1993-10-05</t>
+        </is>
+      </c>
+      <c r="D6" s="260" t="inlineStr">
+        <is>
+          <t>Frontend</t>
+        </is>
+      </c>
+      <c r="E6" s="260" t="inlineStr"/>
+    </row>
+    <row r="7" ht="30" customHeight="1">
       <c r="A7" s="260" t="inlineStr">
         <is>
-          <t>RD-03</t>
+          <t>BD-03</t>
         </is>
       </c>
       <c r="B7" s="260" t="inlineStr">
         <is>
-          <t>Процесс</t>
-        </is>
-      </c>
-      <c r="C7" s="260" t="n">
-        <v>4</v>
-      </c>
-      <c r="D7" s="260" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="8" ht="28" customHeight="1">
+          <t>Кузнецов Д.</t>
+        </is>
+      </c>
+      <c r="C7" s="260" t="inlineStr">
+        <is>
+          <t>1988-11-12</t>
+        </is>
+      </c>
+      <c r="D7" s="260" t="inlineStr">
+        <is>
+          <t>Backend</t>
+        </is>
+      </c>
+      <c r="E7" s="260" t="inlineStr"/>
+    </row>
+    <row r="8" ht="30" customHeight="1">
       <c r="A8" s="260" t="inlineStr">
         <is>
-          <t>RD-04</t>
+          <t>BD-04</t>
         </is>
       </c>
       <c r="B8" s="260" t="inlineStr">
         <is>
-          <t>Инструменты</t>
-        </is>
-      </c>
-      <c r="C8" s="260" t="n">
-        <v>4</v>
-      </c>
-      <c r="D8" s="260" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="9" ht="28" customHeight="1">
+          <t>Орлова Е.</t>
+        </is>
+      </c>
+      <c r="C8" s="260" t="inlineStr">
+        <is>
+          <t>1995-09-28</t>
+        </is>
+      </c>
+      <c r="D8" s="260" t="inlineStr">
+        <is>
+          <t>Analyst</t>
+        </is>
+      </c>
+      <c r="E8" s="260" t="inlineStr"/>
+    </row>
+    <row r="9" ht="30" customHeight="1">
       <c r="A9" s="260" t="inlineStr">
         <is>
-          <t>RD-05</t>
+          <t>BD-05</t>
         </is>
       </c>
       <c r="B9" s="260" t="inlineStr">
         <is>
-          <t>Нагрузка</t>
-        </is>
-      </c>
-      <c r="C9" s="260" t="n">
-        <v>3</v>
-      </c>
-      <c r="D9" s="260" t="n">
-        <v>2</v>
-      </c>
+          <t>Соколов Р.</t>
+        </is>
+      </c>
+      <c r="C9" s="260" t="inlineStr">
+        <is>
+          <t>1991-12-03</t>
+        </is>
+      </c>
+      <c r="D9" s="260" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="E9" s="260" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Планирование_спринта_PRO.xlsx
+++ b/Планирование_спринта_PRO.xlsx
@@ -31,6 +31,7 @@
     <sheet name="Дэйли" sheetId="27" r:id="rId27"/>
     <sheet name="График отпусков" sheetId="28" r:id="rId28"/>
     <sheet name="Дни рождения" sheetId="29" r:id="rId29"/>
+    <sheet name="Контроль scope" sheetId="30" r:id="rId30"/>
   </sheets>
 </workbook>
 </file>
@@ -6494,6 +6495,105 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet30.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ID</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Дата</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Спринт</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Тип</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Задача/элемент</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Что изменилось</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SC-01</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-08-29</t>
+        </is>
+      </c>
+      <c r="C2">
+        <v>2</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Добавлено</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">T-07</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Срочный запрос заказчика добавлен в активный спринт</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SC-02</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-05</t>
+        </is>
+      </c>
+      <c r="C3">
+        <v>3</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Перенесено</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">T-08</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Не поместилось по ёмкости — перенос в следующий спринт</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetData>

--- a/Планирование_спринта_PRO.xlsx
+++ b/Планирование_спринта_PRO.xlsx
@@ -32,6 +32,16 @@
     <sheet name="График отпусков" sheetId="28" r:id="rId28"/>
     <sheet name="Дни рождения" sheetId="29" r:id="rId29"/>
     <sheet name="Контроль scope" sheetId="30" r:id="rId30"/>
+    <sheet name="Запросы на изменение" sheetId="31" r:id="rId31"/>
+    <sheet name="Журнал проблем" sheetId="32" r:id="rId32"/>
+    <sheet name="Стейкхолдеры" sheetId="33" r:id="rId33"/>
+    <sheet name="Журнал решений" sheetId="34" r:id="rId34"/>
+    <sheet name="Импедименты" sheetId="35" r:id="rId35"/>
+    <sheet name="Уроки" sheetId="36" r:id="rId36"/>
+    <sheet name="RACI" sheetId="37" r:id="rId37"/>
+    <sheet name="Story Map" sheetId="38" r:id="rId38"/>
+    <sheet name="Planning Poker" sheetId="39" r:id="rId39"/>
+    <sheet name="Портфель" sheetId="40" r:id="rId40"/>
   </sheets>
 </workbook>
 </file>
@@ -6491,6 +6501,112 @@
         </is>
       </c>
     </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">E-1</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Эпик: Оформление и оплата заказа</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Эпик</t>
+        </is>
+      </c>
+      <c r="F22">
+        <v>0</v>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">В работе</t>
+        </is>
+      </c>
+      <c r="H22">
+        <v>0</v>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">E-2</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Эпик: Каталог и личный кабинет</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Эпик</t>
+        </is>
+      </c>
+      <c r="F23">
+        <v>0</v>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">To Do</t>
+        </is>
+      </c>
+      <c r="H23">
+        <v>0</v>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
   </sheetData>
 </worksheet>
 </file>
@@ -6594,6 +6710,1526 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ID</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Дата</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Запрос</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Тип</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Влияние</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Инициатор</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Статус</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Решение</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CR-01</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-08-30</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Добавить вход через SSO (OAuth2)</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Scope</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">+8 SP, +1 спринт</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Product Owner</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Одобрен</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Включено в релиз R-2</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CR-02</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-08</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Поддержка оплаты в рассрочку</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Scope</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">+13 SP</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Коммерция</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Отложен</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Вернуться после MVP</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CR-03</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-14</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Сдвиг даты релиза на 2 недели</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Срок</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">−1 риск, −ценность</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Спонсор</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Предложен</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Нужно решение CCB</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet32.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ID</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Дата</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Проблема</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Приоритет</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Владелец</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Статус</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Срок</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Решение</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">IS-01</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-05</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Платёжный шлюз возвращает таймауты в песочнице</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">High</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Кузнецов Д.</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">В работе</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-20</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Эскалировано провайдеру</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">IS-02</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-09</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Расхождение остатков каталога с 1С</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Medium</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Орлова Е.</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Открыта</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-25</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">IS-03</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-08-28</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Падение сборки CI на флейки-тестах</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Low</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DevOps</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Решена</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-02</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Карантин флейки-тестов</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet33.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ID</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Стейкхолдер</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Роль</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Влияние</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Интерес</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Вовлечённость</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Целевая</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Стратегия</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SH-01</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Директор по продукту</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Спонсор</t>
+        </is>
+      </c>
+      <c r="D2">
+        <v>5</v>
+      </c>
+      <c r="E2">
+        <v>5</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Поддерживающий</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Лидер</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Еженедельный статус + демо</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SH-02</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Финансовый директор</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Бюджет</t>
+        </is>
+      </c>
+      <c r="D3">
+        <v>5</v>
+      </c>
+      <c r="E3">
+        <v>2</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Нейтральный</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Поддерживающий</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Держать удовлетворённым: отчёт по бюджету</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SH-03</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Служба поддержки</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Операции</t>
+        </is>
+      </c>
+      <c r="D4">
+        <v>2</v>
+      </c>
+      <c r="E4">
+        <v>4</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Поддерживающий</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Поддерживающий</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Информировать о релизах</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SH-04</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Отдел безопасности</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Compliance</t>
+        </is>
+      </c>
+      <c r="D5">
+        <v>4</v>
+      </c>
+      <c r="E5">
+        <v>3</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Сопротивляется</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Нейтральный</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ранние ревью, PCI DSS</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SH-05</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Маркетинг</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Go-to-market</t>
+        </is>
+      </c>
+      <c r="D6">
+        <v>3</v>
+      </c>
+      <c r="E6">
+        <v>5</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Поддерживающий</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Лидер</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Совместное планирование запуска</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet34.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ID</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Дата</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Решение</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Контекст</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Варианты</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Что решили</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Обоснование</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Владелец</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Статус</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DC-01</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-08-12</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PostgreSQL как основная СУБД</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Нужны транзакции и отчётность</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PostgreSQL / MongoDB</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PostgreSQL</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ACID, зрелость, SQL-аналитика</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Архитектор</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Принято</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DC-02</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-08-20</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Двухнедельные спринты</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Баланс обратной связи и накладных</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1 / 2 / 3 недели</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2 недели</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Оптимальный ритм для команды</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Scrum-мастер</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Принято</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DC-03</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-10</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Платёжный провайдер</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Выбор интеграции оплаты</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Провайдер A / B</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Провайдер A (пилот)</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Быстрее интеграция, тест-режим</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Product Owner</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Пересмотрено</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet35.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ID</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Возник</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Импедимент</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Владелец</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Серьёзность</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Статус</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Спринт</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Снят</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">IM-01</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-08</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Нет ключей от платёжного провайдера</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Product Owner</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">High</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">В работе</t>
+        </is>
+      </c>
+      <c r="G2">
+        <v>3</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">IM-02</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-12</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Стенд нестабилен (падает ночью)</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DevOps</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Medium</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Открыт</t>
+        </is>
+      </c>
+      <c r="G3">
+        <v>3</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet36.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ID</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Дата</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Спринт</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Категория</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ситуация</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Урок</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Рекомендация</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LE-01</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-08-29</t>
+        </is>
+      </c>
+      <c r="C2">
+        <v>2</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Процесс</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Недооценили интеграцию оплаты</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Для внешних интеграций нужен спайк</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Добавлять исследовательскую задачу и буфер</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LE-02</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-12</t>
+        </is>
+      </c>
+      <c r="C3">
+        <v>3</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Качество</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Флейки-тесты роняли CI</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Нестабильные тесты дороже, чем кажется</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Карантин флейки-тестов и починка по SLA</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet37.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ID</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Активность</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">R</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">C</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">I</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RA-01</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Планирование спринта</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Команда</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Scrum-мастер</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Product Owner</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Стейкхолдеры</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RA-02</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Приоритизация бэклога</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Product Owner</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Product Owner</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Команда</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ИТ-Лидер</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RA-03</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Релиз в прод</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DevOps</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ИТ-Лидер</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">QA</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Поддержка, PO</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RA-04</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Приёмка на демо</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Product Owner</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Product Owner</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Команда</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Заказчик</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet38.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ID</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Активность</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Релиз</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">История</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Задача</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SM-01</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Выбор товара</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">R-1</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Каталог и карточка товара</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SM-02</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Корзина</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">R-1</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Добавление и редактирование корзины</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">T-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SM-03</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Оформление</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">R-1</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Оформление заказа (MVP)</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">T-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SM-04</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Оплата</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">R-1</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Оплата картой</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">T-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SM-05</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Оформление</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">R-2</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Промокоды и скидки</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SM-06</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Оплата</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">R-2</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Оплата в рассрочку</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SM-07</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">После покупки</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">R-2</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">История заказов и уведомления</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet39.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ID</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Задача</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">История</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Голоса</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Итог</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Статус</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PK-01</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">T-03</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Оплата картой</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Иванов:5, Петрова:8, Кузнецов:8, Орлова:5</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Завершён</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PK-02</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Промокоды и скидки</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Иванов:3, Петрова:5, Кузнецов:8</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Открыт</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetData>
@@ -6851,6 +8487,191 @@
       </c>
       <c r="D14">
         <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet40.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ID</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Проект</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RAG</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Health</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Velocity</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Бюджет</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Потрачено</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Прогресс</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Владелец</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Комментарий</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PO-01</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Маркетплейс (текущий)</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Жёлтый</t>
+        </is>
+      </c>
+      <c r="D2">
+        <v>0.62</v>
+      </c>
+      <c r="E2">
+        <v>34</v>
+      </c>
+      <c r="F2">
+        <v>8000000</v>
+      </c>
+      <c r="G2">
+        <v>3200000</v>
+      </c>
+      <c r="H2">
+        <v>0.45</v>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PMO</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Активный проект</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PO-02</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Мобильное приложение</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Зелёный</t>
+        </is>
+      </c>
+      <c r="D3">
+        <v>0.82</v>
+      </c>
+      <c r="E3">
+        <v>28</v>
+      </c>
+      <c r="F3">
+        <v>5000000</v>
+      </c>
+      <c r="G3">
+        <v>1500000</v>
+      </c>
+      <c r="H3">
+        <v>0.3</v>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mobile Lead</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">По плану</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PO-03</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Миграция в облако</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Красный</t>
+        </is>
+      </c>
+      <c r="D4">
+        <v>0.48</v>
+      </c>
+      <c r="E4">
+        <v>18</v>
+      </c>
+      <c r="F4">
+        <v>6000000</v>
+      </c>
+      <c r="G4">
+        <v>4800000</v>
+      </c>
+      <c r="H4">
+        <v>0.7</v>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Platform</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Перерасход, риск сроков</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/Планирование_спринта_PRO.xlsx
+++ b/Планирование_спринта_PRO.xlsx
@@ -42,6 +42,9 @@
     <sheet name="Story Map" sheetId="38" r:id="rId38"/>
     <sheet name="Planning Poker" sheetId="39" r:id="rId39"/>
     <sheet name="Портфель" sheetId="40" r:id="rId40"/>
+    <sheet name="Team Health Check" sheetId="41" r:id="rId41"/>
+    <sheet name="Деплои" sheetId="42" r:id="rId42"/>
+    <sheet name="Инциденты" sheetId="43" r:id="rId43"/>
   </sheets>
 </workbook>
 </file>
@@ -8678,6 +8681,858 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet41.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ID</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Дата</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Спринт</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Измерение</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Оценка</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Тренд</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Комментарий</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HC-01</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-11</t>
+        </is>
+      </c>
+      <c r="C2">
+        <v>3</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Поставка ценности</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Зелёный</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Растёт</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Регулярные демо принимаются</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HC-02</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-11</t>
+        </is>
+      </c>
+      <c r="C3">
+        <v>3</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Простота работы</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Жёлтый</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Стабильно</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Много ручной рутины</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HC-03</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-11</t>
+        </is>
+      </c>
+      <c r="C4">
+        <v>3</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Обучение</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Зелёный</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Растёт</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Парное программирование</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HC-04</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-11</t>
+        </is>
+      </c>
+      <c r="C5">
+        <v>3</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Миссия</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Зелёный</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Стабильно</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Цель понятна всем</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HC-05</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-11</t>
+        </is>
+      </c>
+      <c r="C6">
+        <v>3</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Командная работа</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Зелёный</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Растёт</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Хорошая взаимопомощь</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HC-06</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-11</t>
+        </is>
+      </c>
+      <c r="C7">
+        <v>3</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Поддержка и помощь</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Жёлтый</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Стабильно</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Внешние зависимости тормозят</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HC-07</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-11</t>
+        </is>
+      </c>
+      <c r="C8">
+        <v>3</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Пешки или игроки</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Зелёный</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Стабильно</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Команда влияет на решения</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HC-08</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-11</t>
+        </is>
+      </c>
+      <c r="C9">
+        <v>3</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Скорость</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Жёлтый</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Падает</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Блокеры по оплате</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HC-09</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-11</t>
+        </is>
+      </c>
+      <c r="C10">
+        <v>3</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Подходящий процесс</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Зелёный</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Стабильно</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Scrum устоялся</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HC-10</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-11</t>
+        </is>
+      </c>
+      <c r="C11">
+        <v>3</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Здоровье кодовой базы</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Красный</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Падает</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Рост техдолга и флейки-тестов</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HC-11</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-11</t>
+        </is>
+      </c>
+      <c r="C12">
+        <v>3</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Весело</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Зелёный</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Стабильно</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Команда мотивирована</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet42.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ID</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Дата</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Релиз</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Среда</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Статус</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Lead time (дн)</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Комментарий</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DP-01</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-08-15</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">R-1</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Prod</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Успех</t>
+        </is>
+      </c>
+      <c r="F2">
+        <v>3</v>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Каркас каталога</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DP-02</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-08-27</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">R-1</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Prod</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Успех</t>
+        </is>
+      </c>
+      <c r="F3">
+        <v>2.2</v>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Корзина</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DP-03</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-02</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">R-1</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Stage</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Успех</t>
+        </is>
+      </c>
+      <c r="F4">
+        <v>1.4</v>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Оплата (пилот)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DP-04</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-09</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">R-1</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Prod</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Откат</t>
+        </is>
+      </c>
+      <c r="F5">
+        <v>2.8</v>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Откат из-за сбоя оплаты</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DP-05</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-10</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">R-1</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Prod</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Успех</t>
+        </is>
+      </c>
+      <c r="F6">
+        <v>0.6</v>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Хотфикс оплаты</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DP-06</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-14</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">R-2</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Prod</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Успех</t>
+        </is>
+      </c>
+      <c r="F7">
+        <v>1.9</v>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Уведомления</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet43.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ID</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Дата</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Инцидент</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Серьёзность</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Восстановление (ч)</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Причина</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Статус</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Постмортем</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">IN-01</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-09</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Массовые таймауты оплаты в проде</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Critical</t>
+        </is>
+      </c>
+      <c r="E2">
+        <v>2.5</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Таймаут платёжного шлюза</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Восстановлен</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Добавить ретраи и circuit breaker</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">IN-02</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-12</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Расхождение остатков каталога</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Medium</t>
+        </is>
+      </c>
+      <c r="E3">
+        <v>6</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Задержка синхронизации с 1С</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Закрыт</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Мониторинг лага синхронизации</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">IN-03</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-15</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Падение уведомлений (email)</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">High</t>
+        </is>
+      </c>
+      <c r="E4">
+        <v>1.2</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Лимит SMTP</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Восстановлен</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Очередь и бэкофф</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetData>

--- a/Планирование_спринта_PRO.xlsx
+++ b/Планирование_спринта_PRO.xlsx
@@ -6610,6 +6610,218 @@
         </is>
       </c>
     </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FE-1</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Фича: Корзина и заказ</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Фича</t>
+        </is>
+      </c>
+      <c r="F24">
+        <v>0</v>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">В работе</t>
+        </is>
+      </c>
+      <c r="H24">
+        <v>0</v>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FE-2</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Фича: Онлайн-оплата</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Фича</t>
+        </is>
+      </c>
+      <c r="F25">
+        <v>0</v>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">В работе</t>
+        </is>
+      </c>
+      <c r="H25">
+        <v>0</v>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FE-3</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Фича: Личный кабинет</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Фича</t>
+        </is>
+      </c>
+      <c r="F26">
+        <v>0</v>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">В работе</t>
+        </is>
+      </c>
+      <c r="H26">
+        <v>0</v>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FE-4</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Фича: Каталог и рекомендации</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Фича</t>
+        </is>
+      </c>
+      <c r="F27">
+        <v>0</v>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">To Do</t>
+        </is>
+      </c>
+      <c r="H27">
+        <v>0</v>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
   </sheetData>
 </worksheet>
 </file>

--- a/Планирование_спринта_PRO.xlsx
+++ b/Планирование_спринта_PRO.xlsx
@@ -45,6 +45,7 @@
     <sheet name="Team Health Check" sheetId="41" r:id="rId41"/>
     <sheet name="Деплои" sheetId="42" r:id="rId42"/>
     <sheet name="Инциденты" sheetId="43" r:id="rId43"/>
+    <sheet name="Гант по иерархии" sheetId="44" r:id="rId44"/>
   </sheets>
 </workbook>
 </file>
@@ -9745,6 +9746,4266 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet44.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Уровень</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ID</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Тип</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Название</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Родитель</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Зависит от</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Исполнитель</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Статус</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Спринт</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">План: начало</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">План: конец</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Факт: начало</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Факт: конец</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Объём, SP</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Готово, SP</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Прогресс</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Просрочено</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Базовый план: начало</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Базовый план: конец</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Сдвиг, дн.</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Прогноз завершения</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Начало бизнес-анализа</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Бизнес-анализ пройден</t>
+        </is>
+      </c>
+      <c r="X1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Начало системного анализа</t>
+        </is>
+      </c>
+      <c r="Y1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Системный анализ пройден</t>
+        </is>
+      </c>
+      <c r="Z1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Начало разработки</t>
+        </is>
+      </c>
+      <c r="AA1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Разработка завершена</t>
+        </is>
+      </c>
+      <c r="AB1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Начало ИФТ (интеграционно-функциональное тестирование)</t>
+        </is>
+      </c>
+      <c r="AC1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ИФТ завершено</t>
+        </is>
+      </c>
+      <c r="AD1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Начало ПСИ (приёмо-сдаточные испытания)</t>
+        </is>
+      </c>
+      <c r="AE1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ПСИ завершено</t>
+        </is>
+      </c>
+      <c r="AF1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Начало выхода в Прод</t>
+        </is>
+      </c>
+      <c r="AG1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Выход в Прод</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">E-1</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Эпик</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Эпик: Оформление и оплата заказа</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">В работе</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">03.08.2026</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11.09.2026</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">03.08.2026</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10.09.2026</t>
+        </is>
+      </c>
+      <c r="N2">
+        <v>53</v>
+      </c>
+      <c r="O2">
+        <v>30</v>
+      </c>
+      <c r="P2">
+        <v>0.57</v>
+      </c>
+      <c r="Q2">
+        <v>1</v>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10.10.2026</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20.07.2026</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">05.08.2026</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">24.07.2026</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">14.08.2026</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">03.08.2026</t>
+        </is>
+      </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="AD2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">14.08.2026</t>
+        </is>
+      </c>
+      <c r="AE2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="AF2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">17.08.2026</t>
+        </is>
+      </c>
+      <c r="AG2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FE-1</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Фича</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Фича: Корзина и заказ</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">E-1</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">В работе</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">03.08.2026</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11.09.2026</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">03.08.2026</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10.09.2026</t>
+        </is>
+      </c>
+      <c r="N3">
+        <v>23</v>
+      </c>
+      <c r="O3">
+        <v>13</v>
+      </c>
+      <c r="P3">
+        <v>0.57</v>
+      </c>
+      <c r="Q3">
+        <v>1</v>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10.10.2026</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20.07.2026</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">24.07.2026</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">24.07.2026</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">31.07.2026</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">03.08.2026</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="AD3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">14.08.2026</t>
+        </is>
+      </c>
+      <c r="AE3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">14.08.2026</t>
+        </is>
+      </c>
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">17.08.2026</t>
+        </is>
+      </c>
+      <c r="AG3" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">T-01</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">История</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Проектирование API заказов</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FE-1</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Иванов А.</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Готово</t>
+        </is>
+      </c>
+      <c r="I4">
+        <v>1</v>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">03.08.2026</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">14.08.2026</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">03.08.2026</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">06.08.2026</t>
+        </is>
+      </c>
+      <c r="N4">
+        <v>5</v>
+      </c>
+      <c r="O4">
+        <v>5</v>
+      </c>
+      <c r="P4">
+        <v>1</v>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">03.08.2026</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">06.08.2026</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="AD4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">14.08.2026</t>
+        </is>
+      </c>
+      <c r="AE4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">14.08.2026</t>
+        </is>
+      </c>
+      <c r="AF4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">17.08.2026</t>
+        </is>
+      </c>
+      <c r="AG4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">28.08.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5">
+        <v>3</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">T-10</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">История</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Модель данных заказа</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FE-1</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Кузнецов Д.</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">В работе</t>
+        </is>
+      </c>
+      <c r="I5">
+        <v>1</v>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">03.08.2026</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11.09.2026</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">05.08.2026</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10.09.2026</t>
+        </is>
+      </c>
+      <c r="N5">
+        <v>10</v>
+      </c>
+      <c r="O5">
+        <v>0</v>
+      </c>
+      <c r="P5">
+        <v>0</v>
+      </c>
+      <c r="Q5">
+        <v>1</v>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">05.08.2026</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="AD5" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="AE5" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="AF5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">17.08.2026</t>
+        </is>
+      </c>
+      <c r="AG5" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6">
+        <v>4</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">T-15</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Задача</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">История заказов</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">T-10</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Соколов Р.</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">To Do</t>
+        </is>
+      </c>
+      <c r="I6">
+        <v>3</v>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">31.08.2026</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11.09.2026</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="N6">
+        <v>5</v>
+      </c>
+      <c r="O6">
+        <v>0</v>
+      </c>
+      <c r="P6">
+        <v>0</v>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="AD6" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="AE6" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="AF6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">14.09.2026</t>
+        </is>
+      </c>
+      <c r="AG6" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7">
+        <v>3</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">T-02</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Задача</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Экран корзины (вёрстка)</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FE-1</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">T-01</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Петрова М.</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Готово</t>
+        </is>
+      </c>
+      <c r="I7">
+        <v>1</v>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">03.08.2026</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">14.08.2026</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">04.08.2026</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">12.08.2026</t>
+        </is>
+      </c>
+      <c r="N7">
+        <v>8</v>
+      </c>
+      <c r="O7">
+        <v>8</v>
+      </c>
+      <c r="P7">
+        <v>1</v>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">04.08.2026</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">12.08.2026</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="AD7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">14.08.2026</t>
+        </is>
+      </c>
+      <c r="AE7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">14.08.2026</t>
+        </is>
+      </c>
+      <c r="AF7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">17.08.2026</t>
+        </is>
+      </c>
+      <c r="AG7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">28.08.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8">
+        <v>2</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FE-2</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Фича</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Фича: Онлайн-оплата</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">E-1</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">В работе</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">17.08.2026</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11.09.2026</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">17.08.2026</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10.09.2026</t>
+        </is>
+      </c>
+      <c r="N8">
+        <v>30</v>
+      </c>
+      <c r="O8">
+        <v>17</v>
+      </c>
+      <c r="P8">
+        <v>0.57</v>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">29.09.2026</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">27.07.2026</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">05.08.2026</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">05.08.2026</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">14.08.2026</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">17.08.2026</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="AD8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">28.08.2026</t>
+        </is>
+      </c>
+      <c r="AE8" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="AF8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">17.08.2026</t>
+        </is>
+      </c>
+      <c r="AG8" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9">
+        <v>3</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">T-11</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">История</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">API промокодов</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FE-2</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Козлов В.</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Готово</t>
+        </is>
+      </c>
+      <c r="I9">
+        <v>2</v>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">17.08.2026</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">28.08.2026</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">17.08.2026</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">26.08.2026</t>
+        </is>
+      </c>
+      <c r="N9">
+        <v>9</v>
+      </c>
+      <c r="O9">
+        <v>9</v>
+      </c>
+      <c r="P9">
+        <v>1</v>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">17.08.2026</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">26.08.2026</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="AD9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">28.08.2026</t>
+        </is>
+      </c>
+      <c r="AE9" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="AF9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">17.08.2026</t>
+        </is>
+      </c>
+      <c r="AG9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">28.08.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10">
+        <v>4</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">T-08</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Задача</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Уведомления по e-mail</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">T-11</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Смирнов П.</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Готово</t>
+        </is>
+      </c>
+      <c r="I10">
+        <v>2</v>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">17.08.2026</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">28.08.2026</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">19.08.2026</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">26.08.2026</t>
+        </is>
+      </c>
+      <c r="N10">
+        <v>4</v>
+      </c>
+      <c r="O10">
+        <v>4</v>
+      </c>
+      <c r="P10">
+        <v>1</v>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">19.08.2026</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">26.08.2026</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="AD10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">28.08.2026</t>
+        </is>
+      </c>
+      <c r="AE10" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="AF10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">17.08.2026</t>
+        </is>
+      </c>
+      <c r="AG10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">28.08.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11">
+        <v>3</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">T-14</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">История</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Вебхуки платежей</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FE-2</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">T-13</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Иванов А.</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">To Do</t>
+        </is>
+      </c>
+      <c r="I11">
+        <v>3</v>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">17.08.2026</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11.09.2026</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">17.08.2026</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">24.08.2026</t>
+        </is>
+      </c>
+      <c r="N11">
+        <v>13</v>
+      </c>
+      <c r="O11">
+        <v>8</v>
+      </c>
+      <c r="P11">
+        <v>0.62</v>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">25.09.2026</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">17.08.2026</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">24.08.2026</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="AD11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">28.08.2026</t>
+        </is>
+      </c>
+      <c r="AE11" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="AF11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">17.08.2026</t>
+        </is>
+      </c>
+      <c r="AG11" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12">
+        <v>4</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">T-03</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Задача</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Интеграция платежей</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">T-14</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">T-01</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Иванов А.</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Готово</t>
+        </is>
+      </c>
+      <c r="I12">
+        <v>2</v>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">17.08.2026</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">28.08.2026</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">17.08.2026</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">24.08.2026</t>
+        </is>
+      </c>
+      <c r="N12">
+        <v>8</v>
+      </c>
+      <c r="O12">
+        <v>8</v>
+      </c>
+      <c r="P12">
+        <v>1</v>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">17.08.2026</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">24.08.2026</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="AD12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">28.08.2026</t>
+        </is>
+      </c>
+      <c r="AE12" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="AF12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">17.08.2026</t>
+        </is>
+      </c>
+      <c r="AG12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">28.08.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13">
+        <v>3</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">T-13</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Задача</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Экран оплаты</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FE-2</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">T-03</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Волкова Н.</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">В работе</t>
+        </is>
+      </c>
+      <c r="I13">
+        <v>3</v>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">31.08.2026</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11.09.2026</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">01.09.2026</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10.09.2026</t>
+        </is>
+      </c>
+      <c r="N13">
+        <v>8</v>
+      </c>
+      <c r="O13">
+        <v>0</v>
+      </c>
+      <c r="P13">
+        <v>0</v>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">01.09.2026</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="AD13" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="AE13" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="AF13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">14.09.2026</t>
+        </is>
+      </c>
+      <c r="AG13" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14">
+        <v>1</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">E-2</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Эпик</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Эпик: Каталог и личный кабинет</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">To Do</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">31.08.2026</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">09.10.2026</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">02.09.2026</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10.09.2026</t>
+        </is>
+      </c>
+      <c r="N14">
+        <v>43</v>
+      </c>
+      <c r="O14">
+        <v>0</v>
+      </c>
+      <c r="P14">
+        <v>0</v>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">02.09.2026</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="AD14" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="AE14" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="AF14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">14.09.2026</t>
+        </is>
+      </c>
+      <c r="AG14" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15">
+        <v>2</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FE-3</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Фича</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Фича: Личный кабинет</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">E-2</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">В работе</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">31.08.2026</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">25.09.2026</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">02.09.2026</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10.09.2026</t>
+        </is>
+      </c>
+      <c r="N15">
+        <v>11</v>
+      </c>
+      <c r="O15">
+        <v>0</v>
+      </c>
+      <c r="P15">
+        <v>0</v>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">02.09.2026</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="AD15" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="AE15" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="AF15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">14.09.2026</t>
+        </is>
+      </c>
+      <c r="AG15" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16">
+        <v>3</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">T-05</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Задача</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Рефакторинг авторизации</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FE-3</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Кузнецов Д.</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">В работе</t>
+        </is>
+      </c>
+      <c r="I16">
+        <v>3</v>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">31.08.2026</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11.09.2026</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">02.09.2026</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10.09.2026</t>
+        </is>
+      </c>
+      <c r="N16">
+        <v>3</v>
+      </c>
+      <c r="O16">
+        <v>0</v>
+      </c>
+      <c r="P16">
+        <v>0</v>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">02.09.2026</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="AD16" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="AE16" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="AF16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">14.09.2026</t>
+        </is>
+      </c>
+      <c r="AG16" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17">
+        <v>3</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">T-16</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Задача</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Личный кабинет</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FE-3</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">T-15</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Волкова Н.</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">To Do</t>
+        </is>
+      </c>
+      <c r="I17">
+        <v>4</v>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">14.09.2026</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">25.09.2026</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="N17">
+        <v>8</v>
+      </c>
+      <c r="O17">
+        <v>0</v>
+      </c>
+      <c r="P17">
+        <v>0</v>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="AD17" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="AE17" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="AF17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">14.09.2026</t>
+        </is>
+      </c>
+      <c r="AG17" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18">
+        <v>2</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FE-4</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Фича</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Фича: Каталог и рекомендации</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">E-2</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">To Do</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">31.08.2026</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">09.10.2026</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="N18">
+        <v>27</v>
+      </c>
+      <c r="O18">
+        <v>0</v>
+      </c>
+      <c r="P18">
+        <v>0</v>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="AD18" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="AE18" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="AF18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">14.09.2026</t>
+        </is>
+      </c>
+      <c r="AG18" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19">
+        <v>3</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">T-06</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">История</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Аналитика воронки</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FE-4</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Орлова Е.</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">To Do</t>
+        </is>
+      </c>
+      <c r="I19">
+        <v>3</v>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">31.08.2026</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11.09.2026</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="N19">
+        <v>3</v>
+      </c>
+      <c r="O19">
+        <v>0</v>
+      </c>
+      <c r="P19">
+        <v>0</v>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="AD19" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="AE19" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="AF19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">14.09.2026</t>
+        </is>
+      </c>
+      <c r="AG19" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20">
+        <v>3</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">T-17</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">История</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Фильтры каталога</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FE-4</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">T-16</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Морозов И.</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">To Do</t>
+        </is>
+      </c>
+      <c r="I20">
+        <v>4</v>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">14.09.2026</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">25.09.2026</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="N20">
+        <v>11</v>
+      </c>
+      <c r="O20">
+        <v>0</v>
+      </c>
+      <c r="P20">
+        <v>0</v>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="AD20" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="AE20" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="AF20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">14.09.2026</t>
+        </is>
+      </c>
+      <c r="AG20" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21">
+        <v>4</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">T-18</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Тех.долг</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Отзывы и рейтинги</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">T-17</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Лебедева Т.</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">To Do</t>
+        </is>
+      </c>
+      <c r="I21">
+        <v>4</v>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">14.09.2026</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">25.09.2026</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="N21">
+        <v>5</v>
+      </c>
+      <c r="O21">
+        <v>0</v>
+      </c>
+      <c r="P21">
+        <v>0</v>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="R21" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="AD21" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="AE21" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="AF21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">14.09.2026</t>
+        </is>
+      </c>
+      <c r="AG21" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22">
+        <v>3</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">T-19</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">История</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Рекомендации</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FE-4</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Фёдорова О.</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">To Do</t>
+        </is>
+      </c>
+      <c r="I22">
+        <v>5</v>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">28.09.2026</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">09.10.2026</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="N22">
+        <v>13</v>
+      </c>
+      <c r="O22">
+        <v>0</v>
+      </c>
+      <c r="P22">
+        <v>0</v>
+      </c>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="R22" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="AD22" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="AE22" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="AF22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">12.10.2026</t>
+        </is>
+      </c>
+      <c r="AG22" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23">
+        <v>4</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">T-20</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Задача</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A/B тесты чекаута</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">T-19</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Морозов И.</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">To Do</t>
+        </is>
+      </c>
+      <c r="I23">
+        <v>5</v>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">28.09.2026</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">09.10.2026</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="N23">
+        <v>5</v>
+      </c>
+      <c r="O23">
+        <v>0</v>
+      </c>
+      <c r="P23">
+        <v>0</v>
+      </c>
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="R23" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="AD23" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="AE23" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="AF23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">12.10.2026</t>
+        </is>
+      </c>
+      <c r="AG23" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24">
+        <v>2</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">T-07</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Задача</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Регресс-тестирование релиза</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">E-2</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">T-04</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Сидоров К.</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">To Do</t>
+        </is>
+      </c>
+      <c r="I24">
+        <v>3</v>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">31.08.2026</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11.09.2026</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="N24">
+        <v>5</v>
+      </c>
+      <c r="O24">
+        <v>0</v>
+      </c>
+      <c r="P24">
+        <v>0</v>
+      </c>
+      <c r="Q24" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="R24" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="AD24" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="AE24" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="AF24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">14.09.2026</t>
+        </is>
+      </c>
+      <c r="AG24" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25">
+        <v>1</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">T-09</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Задача</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Настройка CI/CD</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Новиков А.</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Готово</t>
+        </is>
+      </c>
+      <c r="I25">
+        <v>1</v>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">03.08.2026</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">14.08.2026</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">03.08.2026</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">05.08.2026</t>
+        </is>
+      </c>
+      <c r="N25">
+        <v>4</v>
+      </c>
+      <c r="O25">
+        <v>4</v>
+      </c>
+      <c r="P25">
+        <v>1</v>
+      </c>
+      <c r="Q25" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="R25" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="S25" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">03.08.2026</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">05.08.2026</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="AD25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">14.08.2026</t>
+        </is>
+      </c>
+      <c r="AE25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">14.08.2026</t>
+        </is>
+      </c>
+      <c r="AF25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">17.08.2026</t>
+        </is>
+      </c>
+      <c r="AG25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">28.08.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26">
+        <v>1</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">T-04</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Тех.долг</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Тест-кейсы оформления</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Сидоров К.</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Готово</t>
+        </is>
+      </c>
+      <c r="I26">
+        <v>2</v>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">17.08.2026</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">28.08.2026</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">18.08.2026</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20.08.2026</t>
+        </is>
+      </c>
+      <c r="N26">
+        <v>4</v>
+      </c>
+      <c r="O26">
+        <v>4</v>
+      </c>
+      <c r="P26">
+        <v>1</v>
+      </c>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="R26" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">18.08.2026</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20.08.2026</t>
+        </is>
+      </c>
+      <c r="AD26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">28.08.2026</t>
+        </is>
+      </c>
+      <c r="AE26" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="AF26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">17.08.2026</t>
+        </is>
+      </c>
+      <c r="AG26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">28.08.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27">
+        <v>1</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">T-12</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Задача</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Логирование и метрики</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Новиков А.</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">To Do</t>
+        </is>
+      </c>
+      <c r="I27">
+        <v>2</v>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">17.08.2026</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">28.08.2026</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="N27">
+        <v>3</v>
+      </c>
+      <c r="O27">
+        <v>0</v>
+      </c>
+      <c r="P27">
+        <v>0</v>
+      </c>
+      <c r="Q27">
+        <v>1</v>
+      </c>
+      <c r="R27" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="AD27" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="AE27" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="AF27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">17.08.2026</t>
+        </is>
+      </c>
+      <c r="AG27" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetData>
